--- a/output/test_alt_abbrev_annotation_with_prompt_using_fulltext_and_abstract_df.xlsx
+++ b/output/test_alt_abbrev_annotation_with_prompt_using_fulltext_and_abstract_df.xlsx
@@ -572,44 +572,42 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>36612533</t>
-        </is>
+      <c r="H2" t="n">
+        <v>7479945</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>mouse phenotype biomarker</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>primer</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>methods</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>The primers were as follows: forward primer RD5 5_-ATC TGG TTG ATC CTG CCA GT-3_ and reverse primer BhRDr 5_-GAG CTT TTTA ACT GCA ACA ACG-3_</t>
+          <t>We report a mouse model of type I Usher syndrome, rd5, whose linkage on mouse chromosome 7 to Hbb and tub has homology to human Usher I reported on human chromosome 11p15. The electroretinogram in homozygous rd5/rd5 mouse is never normal with reduced amplitudes that extinguish by 6 months.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -618,70 +616,16 @@
           <t>TUB bipartite transcription factor</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Blastocystisis one of the most common enteric protozoa that inhabits the intestinal tract of humans and different animals. Moreover, it has a worldwide geographic distribution. Its main mode of transmission is via the fecal-oral route. At present, 26 subtypes are widely distributed across both humans and animals. The current study aimed to determine the prevalence and subtype distribution ofBlastocystisamong school-aged children living on the Thai-Myanmar border, Ratchaburi province, Thailand. In total, 508 samples were collected from children at six schools. The prevalence ofBlastocystisinfection was amplified and sequenced in the 600 bp barcode region of the small-subunit ribosomal RNA (SSU rRNA). The overall prevalence ofBlastocystisinfection was 3.35% (17/508). ST3 (11/17) was the most predominant subtype, followed by ST1 (5/17) and ST2 (1/17). A phylogenetic tree was constructed based on the Tamura92+G+I model using the maximum-likelihood algorithm. Surprisingly, all sequences of the ST3-positive samples were closely correlated with the cattle-derived sequence. Meanwhile, all sequences of theBlastocystisST1-positive samples were closely correlated with the human-derived sequence. Nevertheless, further studies should be conducted to validate the zoonotic transmission ofBlastocystis. Based on our findings, personal hygiene and sanitation should be improved to promote better health in children in this area.
-Intestinal parasitic infections are one of the main public health issues worldwide, and their incidence is higher in developing than in developed countries [1,2].Blastocystisis a common enteric protozoan causing parasitic intestinal infections among children. Further, it mainly colonizes the gastrointestinal tract, and it is transmitted via the fecal-oral route [3,4]. At present, approximately more than 1 billion humans are infected withBlastocystisworldwide [5]. Its transmission is correlated with several factors, such as poor personal hygiene, consumption of contaminated food, and environmental conditions associated with poor quality of life [6,7,8]. Moreover, close contact with animals due to cultural conditions may causeBlastocystisinfection [9,10,11]. Additionally, school-aged children are at high risk ofBlastocystisinfection due to poor hygiene habits [1,4]. Several studies showed that the prevalence ofBlastocystisinfection varies from 0.7% to 45.2% among school-aged children in Thailand [12,13,14,15]. At present, 26 subtypes ofBlastocystisare widely distributed in both humans and animals. Among them, subtype 3 is most commonly observed in humans [16,17]. The methods used to detectBlastocystisare usually based on microscopy. However, these techniques have low sensitivity and specificity, and assessment using these strategies should be performed by skilled microscopists to validate morphology [18,19,20]. In recent years, polymerase chain reaction (PCR), a molecular biology technique, targets a region of the SSU rRNA genes. Moreover, it has the highest sensitivity and specificity and can identify different subtypes [21,22,23]. However, studies on the incidence and subtypes ofBlastocystisin school-aged children living in the border areas of Thailand are limited. The current study aimed to determine the prevalence and subtype distribution ofBlastocystisisolated from school-aged children living in the Thai-Myanmar border areas, Ratchaburi Province, Thailand.
-This cross-sectional study included children aged 4–12 years from six primary schools in Suan Pheung district, Ratchaburi province, near the Thai-Myanmar border, a natural border in western Thailand (Figure 1). Ratchaburi province is divided into 10 districts. Suan Pheung district, which has important natural resources, is the most popular. The forest covers an area of 1711 km2, or 33% of the provincial area. The area is part of the Tenasserim Hills and the Tanintharyi division of Myanmar. The population in this area have low income and education levels. Most people are agriculture employees and construction laborers and some are unemployed. They commonly consume rainwater, stream water, and water from community wells. Fecal samples were collected from children from HP School, TKL School, RJ School, TMK School, SP School, and BW School, which are located in different sub-districts and are all government primary schools.
-The study protocol was approved by the Ethics Committee of the Faculty of Tropical Medicine, Mahidol University (MUTM: 2022-011-01). All fecal samples were collected from both boys and girls. The participants were commonly from the Kayin, Kayar, and Mon ethnic groups. They were aged between 4–12 years and were in kindergarten and grades 1–3. All participants were instructed to ask permission from their parents, and a written informed consent form was obtained before study participation. Children who were not allowed by their parents to join the research were excluded. In total, 508 fecal samples (n= 270, boys andn= 238, girls) were collected. Moreover, according to the schools, the numbers of samples collected were as follows: 98, TKL; 170, HP; 74, TMK; 96, SP; 47, BW; and 23, RJ. There was no substantial difference in the dates of fecal collection among schools. A single sample was collected from each participant. All participants were instructed to collect fecal samples properly. Clean and labeled plastic containers, toilet tissue paper, and applicator sticks were provided. During transportation, the fecal samples were kept preserved at −20 °C until DNA extraction.
-DNA was extracted from all fecal samples using a commercially available DNA extraction kit (PSP Spin Stool Kit, Stractec Molecular, Berlin, Germany), according to the manufacturer’s instructions. All extracted DNAs from fecal samples were stored at −20 °C until conventional PCR. The primers amplified ~600 bp of the SSU rRNA gene. The primers were as follows: forward primer RD5 5′-ATC TGG TTG ATC CTG CCA GT-3′ and reverse primer BhRDr 5′-GAG CTT TTTA ACT GCA ACA ACG-3′ [23]. The 25 µL reaction in each mixture tube contained 1x PCR buffer, 1.5 mM MgCl2, 0.2 mM dNTPs, 1 µM of each primer, and 2.5 UTaqDNA polymerase (Fermentus, Waltham, MA, USA). The PCR conditions were as follows: 1 cycle denaturing step at 94 °C for 3 min, followed by 35 cycles of annealing step at 59 °C for 1 min, and extension step at 72 °C for 1 min. The last cycle was extended for 5 min at 72 °C. The PCR product and 100bp DNA marker was run on 1.5% agarose gel electrophoresis using 1% tris-acetate-EDTA, which is a running buffer. The gel was stained with Hydra green and visualized under an ultraviolet transilluminator.
-Blastocystis-positive samples were sequenced on an ABI 3730x1 automated DNA sequencer. The nucleotide sequences were aligned and compared with reference sequences available in the GenBank database using BLAST (http://blast.ncbi.nlm.nih.gov/, accessed on 5 May 2022) for subtype identification.The blastocystis18S allele database was tested athttp://pubmlst.org/blastocystis/, accessed on 10 May 2022). All 17 nucleotide sequences and reference sequences (ST1-ST17) were manually edited using BioEdit version 7.2.5 (Ibis Biosciences, Inc., Carlsbad, CA, USA) and multiply aligned using the ClustalW programs. Phylogenetic analysis was performed using MEGA version 7. A phylogenetic tree was constructed using the Tamura92+G+I model with the maximum-likelihood algorithm and was tested with 1000 bootstrap replicates.
-Descriptive analysis was performed to express the percentages of the positive samples ofBlastocystis. The chi-square test was used to compareBlastocystisprevalence according to age and sex. Ap-value of &lt;0.05 was considered statistically significant.
-The prevalence rate ofBlastocystisinfection was 3.35% (17/508) based on the assessment performed using PCR, as shown inTable 1. According to the schools, the prevalence rate was 7.14% (7/98) in TKL, 5.40% (4/74) in TMK, 2.35% (4/170) in HP, 2.13% (1/47) in BW, 1.04% (1/96) in SP, and 0% (0/23%) in RJ.
-The subtype ofBlastocystiswas determined via direct sequencing of the barcode region of the 18S rRNA gene. ST1, ST2, and ST3 were found inBlastocystis-positive fecal samples. ST3 was the predominant subtype (64.71%; 11/17), followed by ST1 (29.41%; 5/17) and ST2 (5.88%; 1/17). TheBlastocystisprevalence was classified according to sex male and female;χ2= 0.096, df= 2,p &gt;0.05) and age ≤6 and &gt;6 years;χ2= 0.145, df= 2,p&gt; 0.05). Results showed that there were no significant differences in theBlastocystisprevalence between sex and age.
-The 17 nucleotide sequences of the barcode region of the SSU rRNA gene were significantly similar (≥98%) to the references ofBlastocystisdeposited in the GenBank databaseTable 2. Results showed that the nucleotide sequence samples belong to the three district subtypes: ST3: TKL25, TKL58, TKL85, TKL95, TKL98, HP83, TMK10, TMK33, TMK69, and BW38; ST1: TKL67, TKL89, HP110, HP161, TMK55, and SP4; and ST2: HP95. The phylogenic tree of the 17 nucleotide sequence samples and the 17 reference sequences in each subtype in the GenBank database was constructed based on the Tamura92+G+I model using the maximum-likelihood algorithm.Proteromonas lacerate(U37108) andKarotomorphaspp. (DQ431242) were classified under the out-group. The sequence ofBlastocystisST1-positive samples was closely correlated with human-derived sequences in the GenBank database. Moreover, the sequence of theBlastocystisST3-positive samples was closely correlated with that of the cattle-derived sequences in the GenBank database, as shown inFigure 2.
-Blastocystisis one of the most common intestinal protozoa that can infect both humans and animals, and it has a worldwide geographic distribution. The current study aimed to assess the prevalence and subtype distribution ofBlastocystisin school-aged children living in the Thai-Myanmar border area. The present study showed a rather low prevalence ofBlastocystisinfection but higher than the study conducted on Thailand’s school children, such as in the Kanchanaburi provinces in the western region of Thailand [24]. It might be different from the method of detection and study population. In Thailand, the prevalence rates ofBlastocystisinfection are 0.7% to 45.2% in school-aged children and the highest infection in young children living in orphan homes in Pathum Thani province [12,13,14,15]. Several studies reported that the prevalence ofBlastocystisinfection was higher in developing countries than in developed countries. Moreover, the prevalence varies from 0.5% to 30% in developed countries, and it is as high as 100% in developing countries [25,26,27,28,29,30].
-The border area in some countries is predominantly rural, people live in poverty, and they lack education. Moreover, its economic development is low [31,32], and the open-defecation behavior of people in this region is attributed to a lack of latrines and water; hence, they are at risk of infection [31,32]. The prevalence rates ofBlastocystisare 37.2% on the Thai-Myanmar border and 6.29% on the China-Myanmar border. The infection is correlated with poor hygiene habits and sanitation in the communities, zoonotic transmission, person-to-person contamination, and consumption of contaminated water [31,32]. However, in this study, the prevalence ofBlastocystisinfection was low. This might be attributed to improvements in common living conditions and easy access to healthcare services, which are attributed to economic growth. Generally, children in this area are not Thai. Most of them are Kayin, Kayar, and Mon. They have access to education and have more opportunities for learning and healthy living. This might explain why the prevalence ofBlastocystisinfection was low.
-Several methods are used for detectingBlastocystisin routine parasitology laboratory examinations, and these include microscopy, xenic in-vitro culture, and molecular biology-based techniques [18,19,20]. Detection is commonly based on microscopy. However, this method has low sensitivity and specificity. It may lead to underdiagnosis and false-positive or false-negative results. The assessment using this strategy should be performed by skilled microscopists to confirm the morphology [18,19,20]. Previous studies have shown that PCR is a rapid and effective method for identifying microorganisms. Further, it can be used for epidemiological studies with a large number of samples [33]. In this study, PCR and the direct sequence technique were applied to detect the subtype ofBlastocystisusing 600 bp of the barcode region. This is the best representative in public databases, and it can be utilized for the analysis of 18S alleles to identify intrasubtype genetic variations [23]. Currently, 26 subtypes ofBlastocystishave been identified in humans and animals [16,34]. ST1-ST4 are the most common subtypes found in humans, and they can occur worldwide [35,36]. This study showed that ST3 was the predominant subtype in boys and girls, followed by ST1 and ST2. This result was similar to that of previous studies in Thailand [35,36] and others in different countries, such as Malaysia [37], Turkey [38], Peru [39], and Italy [40]. Our finding showed 18S alleles ofBlastocystisin each ST, which include allele 4 (ST1), allele 9 (ST2), and alleles 34 and 37 (ST3). Moreover, allele 4 (ST1) is closely correlated with person-to-person transmission [41]. Our result followed that of a previous study on young children from daycare centers because children are less careful about their personal hygiene, leading to more person-to-person transmission [41]. Additionally, allele 9 was most prevalent in both humans and animals, and it might be correlated with zoonotic transmission [42]. Moreover, allele 34 was the predominant allele in non-human primates, such as cattle, thus indicating the possibility of non-host specificity [43]. The parents of most children were agriculture and animal-care workers. Hence, children could have close contact with animals that may cause zoonotic infection. Nevertheless, the main point ofBlastocystisinfection in children commonly depends on personal hygiene habits and sanitation. However, allele analysis can provide useful information about host specificity and geographic distribution, which can lead to a better understanding ofBlastocystistransmission [42,43]. This study did not show a significant difference in the prevalence ofBlastocystisinfection according to age and sex, which was similar to the finding of the previous studies [44,45].
-Based on the phylogenetic trees of the 17 nucleotide sequences collected from the samples, this protozoan belonged to the ST1, ST2, and ST3 subtypes. Surprisingly, our findings revealed that the nucleotide sequence samples of ST3 were closely correlated with the cattle-derived sequence of the reference sequence (GenBank database). Meanwhile, the nucleotide sequence samples of ST1 were significantly with human-derived sequences in the reference sequence (GenBank database). However, our findings ofBlastocystisST3 might be transmitted from animals to humans, which indicates a zoonotic transmission pattern in this area [23].
-This study is the first regarding the prevalence and subtype distribution ofBlastocystissp. in school-aged children living in the Thai-Myanmar border area, Ratchaburi Province, western Thailand. The prevalence ofBlastocystisinfection was quite low in school-aged children. However, the zoonotic potential is considered inBlastocystisST3 infection. Moreover, the transmission ofBlastocystisinfection between humans to humans should not be disregarded. In this study, no questionnaire was used to assess potential sources of infection. More robust approaches must be carried out to determine possible sources of infection. The risk factors that be studied include the use of unsafe water supplies in the locality, domestic and wild animals in the area, as well as transmission in the households of the school children. Moreover, personal hygiene habits should be improved to promote better health and quality of life among children. Further, the disposal of animal and human wastes should be managed properly.
-The authors would like to thank all students who participated in the study and all teachers for their assistance in the collection. We thank the staff of the Protozoology Department, Faculty of Tropical Medicine, Mahidol University, for excellent laboratory assistance.
-Disclaimer/Publisher’s Note:The statements, opinions and data contained in all publications are solely those of the individual author(s) and contributor(s) and not of MDPI and/or the editor(s). MDPI and/or the editor(s) disclaim responsibility for any injury to people or property resulting from any ideas, methods, instructions or products referred to in the content.
-Conceptualization, A.A. and S.P.; methodology, A.A., S.P., C.S., N.S. and D.A.; investigation, A.A.; software, A.A., A.M. and S.P.; validation, A.A.; formal analysis, A.A., K.K., R.C. and S.P.; writing—original draft preparation, A.A.; writing—review and editing, A.A., D.A., N.S., A.M., C.S., K.K., R.C. and S.P.; funding acquisition, D.A. and S.P.; supervision, S.P. All authors have read and agreed to the published version of the manuscript.
-The study was conducted following the Declaration of Helsinki and approved by the Institutional Review Board of the Faculty of Tropical Medicine, Mahidol University (MUTM 2022-011-01) approved on 15 February 2022 for studies involving humans.
-Informed consent was obtained from all subjects involved in the study.
-Not applicable.
-The authors declare no conflict of interest.
-Map of the study area (modified from Wikipedia, 2010).
-A phylogenic tree of the 17 nucleotide sequences was constructed based on theTamura92+G+I model using the maximum-likelihood algorithm.
-Prevalence ofBlastocystisinfection in school-aged children.
-Accession numbers of positive samples used in the phylogenetic reconstruction.</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Blastocystis&lt;/i&gt; is one of the most common enteric protozoa that inhabits the intestinal tract of humans and different animals. Moreover, it has a worldwide geographic distribution. Its main mode of transmission is via the fecal-oral route. At present, 26 subtypes are widely distributed across both humans and animals. The current study aimed to determine the prevalence and subtype distribution of &lt;i&gt;Blastocystis&lt;/i&gt; among school-aged children living on the Thai-Myanmar border, Ratchaburi province, Thailand. In total, 508 samples were collected from children at six schools. The prevalence of &lt;i&gt;Blastocystis&lt;/i&gt; infection was amplified and sequenced in the 600 bp barcode region of the small-subunit ribosomal RNA (SSU rRNA). The overall prevalence of &lt;i&gt;Blastocystis&lt;/i&gt; infection was 3.35% (17/508). ST3 (11/17) was the most predominant subtype, followed by ST1 (5/17) and ST2 (1/17). A phylogenetic tree was constructed based on the Tamura92+G+I model using the maximum-likelihood algorithm. Surprisingly, all sequences of the ST3-positive samples were closely correlated with the cattle-derived sequence. Meanwhile, all sequences of the &lt;i&gt;Blastocystis&lt;/i&gt; ST1-positive samples were closely correlated with the human-derived sequence. Nevertheless, further studies should be conducted to validate the zoonotic transmission of &lt;i&gt;Blastocystis&lt;/i&gt;. Based on our findings, personal hygiene and sanitation should be improved to promote better health in children in this area.</t>
+          <t>Usher syndrome is a group of diseases with autosomal recessive inheritance, congenital hearing loss, and the development of retinitis pigmentosa, a progressive retinal degeneration characterized by night blindness and visual field loss over several decades. The causes of Usher syndrome are unknown and no animal models have been available for study. Four human gene sites have been reported, suggesting at least four separate forms of Usher syndrome. We report a mouse model of type I Usher syndrome, rd5, whose linkage on mouse chromosome 7 to Hbb and tub has homology to human Usher I reported on human chromosome 11p15. The electroretinogram in homozygous rd5/rd5 mouse is never normal with reduced amplitudes that extinguish by 6 months. Auditory-evoked response testing demonstrates increased hearing thresholds more than control at 3 weeks of about 30 decibels (dB) that worsen to about 45 dB by 6 months.</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>PMID: 36612533
-Full Text: Blastocystisis one of the most common enteric protozoa that inhabits the intestinal tract of humans and different animals. Moreover, it has a worldwide geographic distribution. Its main mode of transmission is via the fecal-oral route. At present, 26 subtypes are widely distributed across both humans and animals. The current study aimed to determine the prevalence and subtype distribution ofBlastocystisamong school-aged children living on the Thai-Myanmar border, Ratchaburi province, Thailand. In total, 508 samples were collected from children at six schools. The prevalence ofBlastocystisinfection was amplified and sequenced in the 600 bp barcode region of the small-subunit ribosomal RNA (SSU rRNA). The overall prevalence ofBlastocystisinfection was 3.35% (17/508). ST3 (11/17) was the most predominant subtype, followed by ST1 (5/17) and ST2 (1/17). A phylogenetic tree was constructed based on the Tamura92+G+I model using the maximum-likelihood algorithm. Surprisingly, all sequences of the ST3-positive samples were closely correlated with the cattle-derived sequence. Meanwhile, all sequences of theBlastocystisST1-positive samples were closely correlated with the human-derived sequence. Nevertheless, further studies should be conducted to validate the zoonotic transmission ofBlastocystis. Based on our findings, personal hygiene and sanitation should be improved to promote better health in children in this area.
-Intestinal parasitic infections are one of the main public health issues worldwide, and their incidence is higher in developing than in developed countries [1,2].Blastocystisis a common enteric protozoan causing parasitic intestinal infections among children. Further, it mainly colonizes the gastrointestinal tract, and it is transmitted via the fecal-oral route [3,4]. At present, approximately more than 1 billion humans are infected withBlastocystisworldwide [5]. Its transmission is correlated with several factors, such as poor personal hygiene, consumption of contaminated food, and environmental conditions associated with poor quality of life [6,7,8]. Moreover, close contact with animals due to cultural conditions may causeBlastocystisinfection [9,10,11]. Additionally, school-aged children are at high risk ofBlastocystisinfection due to poor hygiene habits [1,4]. Several studies showed that the prevalence ofBlastocystisinfection varies from 0.7% to 45.2% among school-aged children in Thailand [12,13,14,15]. At present, 26 subtypes ofBlastocystisare widely distributed in both humans and animals. Among them, subtype 3 is most commonly observed in humans [16,17]. The methods used to detectBlastocystisare usually based on microscopy. However, these techniques have low sensitivity and specificity, and assessment using these strategies should be performed by skilled microscopists to validate morphology [18,19,20]. In recent years, polymerase chain reaction (PCR), a molecular biology technique, targets a region of the SSU rRNA genes. Moreover, it has the highest sensitivity and specificity and can identify different subtypes [21,22,23]. However, studies on the incidence and subtypes ofBlastocystisin school-aged children living in the border areas of Thailand are limited. The current study aimed to determine the prevalence and subtype distribution ofBlastocystisisolated from school-aged children living in the Thai-Myanmar border areas, Ratchaburi Province, Thailand.
-This cross-sectional study included children aged 4–12 years from six primary schools in Suan Pheung district, Ratchaburi province, near the Thai-Myanmar border, a natural border in western Thailand (Figure 1). Ratchaburi province is divided into 10 districts. Suan Pheung district, which has important natural resources, is the most popular. The forest covers an area of 1711 km2, or 33% of the provincial area. The area is part of the Tenasserim Hills and the Tanintharyi division of Myanmar. The population in this area have low income and education levels. Most people are agriculture employees and construction laborers and some are unemployed. They commonly consume rainwater, stream water, and water from community wells. Fecal samples were collected from children from HP School, TKL School, RJ School, TMK School, SP School, and BW School, which are located in different sub-districts and are all government primary schools.
-The study protocol was approved by the Ethics Committee of the Faculty of Tropical Medicine, Mahidol University (MUTM: 2022-011-01). All fecal samples were collected from both boys and girls. The participants were commonly from the Kayin, Kayar, and Mon ethnic groups. They were aged between 4–12 years and were in kindergarten and grades 1–3. All participants were instructed to ask permission from their parents, and a written informed consent form was obtained before study participation. Children who were not allowed by their parents to join the research were excluded. In total, 508 fecal samples (n= 270, boys andn= 238, girls) were collected. Moreover, according to the schools, the numbers of samples collected were as follows: 98, TKL; 170, HP; 74, TMK; 96, SP; 47, BW; and 23, RJ. There was no substantial difference in the dates of fecal collection among schools. A single sample was collected from each participant. All participants were instructed to collect fecal samples properly. Clean and labeled plastic containers, toilet tissue paper, and applicator sticks were provided. During transportation, the fecal samples were kept preserved at −20 °C until DNA extraction.
-DNA was extracted from all fecal samples using a commercially available DNA extraction kit (PSP Spin Stool Kit, Stractec Molecular, Berlin, Germany), according to the manufacturer’s instructions. All extracted DNAs from fecal samples were stored at −20 °C until conventional PCR. The primers amplified ~600 bp of the SSU rRNA gene. The primers were as follows: forward primer RD5 5′-ATC TGG TTG ATC CTG CCA GT-3′ and reverse primer BhRDr 5′-GAG CTT TTTA ACT GCA ACA ACG-3′ [23]. The 25 µL reaction in each mixture tube contained 1x PCR buffer, 1.5 mM MgCl2, 0.2 mM dNTPs, 1 µM of each primer, and 2.5 UTaqDNA polymerase (Fermentus, Waltham, MA, USA). The PCR conditions were as follows: 1 cycle denaturing step at 94 °C for 3 min, followed by 35 cycles of annealing step at 59 °C for 1 min, and extension step at 72 °C for 1 min. The last cycle was extended for 5 min at 72 °C. The PCR product and 100bp DNA marker was run on 1.5% agarose gel electrophoresis using 1% tris-acetate-EDTA, which is a running buffer. The gel was stained with Hydra green and visualized under an ultraviolet transilluminator.
-Blastocystis-positive samples were sequenced on an ABI 3730x1 automated DNA sequencer. The nucleotide sequences were aligned and compared with reference sequences available in the GenBank database using BLAST (http://blast.ncbi.nlm.nih.gov/, accessed on 5 May 2022) for subtype identification.The blastocystis18S allele database was tested athttp://pubmlst.org/blastocystis/, accessed on 10 May 2022). All 17 nucleotide sequences and reference sequences (ST1-ST17) were manually edited using BioEdit version 7.2.5 (Ibis Biosciences, Inc., Carlsbad, CA, USA) and multiply aligned using the ClustalW programs. Phylogenetic analysis was performed using MEGA version 7. A phylogenetic tree was constructed using the Tamura92+G+I model with the maximum-likelihood algorithm and was tested with 1000 bootstrap replicates.
-Descriptive analysis was performed to express the percentages of the positive samples ofBlastocystis. The chi-square test was used to compareBlastocystisprevalence according to age and sex. Ap-value of &lt;0.05 was considered statistically significant.
-The prevalence rate ofBlastocystisinfection was 3.35% (17/508) based on the assessment performed using PCR, as shown inTable 1. According to the schools, the prevalence rate was 7.14% (7/98) in TKL, 5.40% (4/74) in TMK, 2.35% (4/170) in HP, 2.13% (1/47) in BW, 1.04% (1/96) in SP, and 0% (0/23%) in RJ.
-The subtype ofBlastocystiswas determined via direct sequencing of the barcode region of the 18S rRNA gene. ST1, ST2, and ST3 were found inBlastocystis-positive fecal samples. ST3 was the predominant subtype (64.71%; 11/17), followed by ST1 (29.41%; 5/17) and ST2 (5.88%; 1/17). TheBlastocystisprevalence was classified according to sex male and female;χ2= 0.096, df= 2,p &gt;0.05) and age ≤6 and &gt;6 years;χ2= 0.145, df= 2,p&gt; 0.05). Results showed that there were no significant differences in theBlastocystisprevalence between sex and age.
-The 17 nucleotide sequences of the barcode region of the SSU rRNA gene were significantly similar (≥98%) to the references ofBlastocystisdeposited in the GenBank databaseTable 2. Results showed that the nucleotide sequence samples belong to the three district subtypes: ST3: TKL25, TKL58, TKL85, TKL95, TKL98, HP83, TMK10, TMK33, TMK69, and BW38; ST1: TKL67, TKL89, HP110, HP161, TMK55, and SP4; and ST2: HP95. The phylogenic tree of the 17 nucleotide sequence samples and the 17 reference sequences in each subtype in the GenBank database was constructed based on the Tamura92+G+I model using the maximum-likelihood algorithm.Proteromonas lacerate(U37108) andKarotomorphaspp. (DQ431242) were classified under the out-group. The sequence ofBlastocystisST1-positive samples was closely correlated with human-derived sequences in the GenBank database. Moreover, the sequence of theBlastocystisST3-positive samples was closely correlated with that of the cattle-derived sequences in the GenBank database, as shown inFigure 2.
-Blastocystisis one of the most common intestinal protozoa that can infect both humans and animals, and it has a worldwide geographic distribution. The current study aimed to assess the prevalence and subtype distribution ofBlastocystisin school-aged children living in the Thai-Myanmar border area. The present study showed a rather low prevalence ofBlastocystisinfection but higher than the study conducted on Thailand’s school children, such as in the Kanchanaburi provinces in the western region of Thailand [24]. It might be different from the method of detection and study population. In Thailand, the prevalence rates ofBlastocystisinfection are 0.7% to 45.2% in school-aged children and the highest infection in young children living in orphan homes in Pathum Thani province [12,13,14,15]. Several studies reported that the prevalence ofBlastocystisinfection was higher in developing countries than in developed countries. Moreover, the prevalence varies from 0.5% to 30% in developed countries, and it is as high as 100% in developing countries [25,26,27,28,29,30].
-The border area in some countries is predominantly rural, people live in poverty, and they lack education. Moreover, its economic development is low [31,32], and the open-defecation behavior of people in this region is attributed to a lack of latrines and water; hence, they are at risk of infection [31,32]. The prevalence rates ofBlastocystisare 37.2% on the Thai-Myanmar border and 6.29% on the China-Myanmar border. The infection is correlated with poor hygiene habits and sanitation in the communities, zoonotic transmission, person-to-person contamination, and consumption of contaminated water [31,32]. However, in this study, the prevalence ofBlastocystisinfection was low. This might be attributed to improvements in common living conditions and easy access to healthcare services, which are attributed to economic growth. Generally, children in this area are not Thai. Most of them are Kayin, Kayar, and Mon. They have access to education and have more opportunities for learning and healthy living. This might explain why the prevalence ofBlastocystisinfection was low.
-Several methods are used for detectingBlastocystisin routine parasitology laboratory examinations, and these include microscopy, xenic in-vitro culture, and molecular biology-based techniques [18,19,20]. Detection is commonly based on microscopy. However, this method has low sensitivity and specificity. It may lead to underdiagnosis and false-positive or false-negative results. The assessment using this strategy should be performed by skilled microscopists to confirm the morphology [18,19,20]. Previous studies have shown that PCR is a rapid and effective method for identifying microorganisms. Further, it can be used for epidemiological studies with a large number of samples [33]. In this study, PCR and the direct sequence technique were applied to detect the subtype ofBlastocystisusing 600 bp of the barcode region. This is the best representative in public databases, and it can be utilized for the analysis of 18S alleles to identify intrasubtype genetic variations [23]. Currently, 26 subtypes ofBlastocystishave been identified in humans and animals [16,34]. ST1-ST4 are the most common subtypes found in humans, and they can occur worldwide [35,36]. This study showed that ST3 was the predominant subtype in boys and girls, followed by ST1 and ST2. This result was similar to that of previous studies in Thailand [35,36] and others in different countries, such as Malaysia [37], Turkey [38], Peru [39], and Italy [40]. Our finding showed 18S alleles ofBlastocystisin each ST, which include allele 4 (ST1), allele 9 (ST2), and alleles 34 and 37 (ST3). Moreover, allele 4 (ST1) is closely correlated with person-to-person transmission [41]. Our result followed that of a previous study on young children from daycare centers because children are less careful about their personal hygiene, leading to more person-to-person transmission [41]. Additionally, allele 9 was most prevalent in both humans and animals, and it might be correlated with zoonotic transmission [42]. Moreover, allele 34 was the predominant allele in non-human primates, such as cattle, thus indicating the possibility of non-host specificity [43]. The parents of most children were agriculture and animal-care workers. Hence, children could have close contact with animals that may cause zoonotic infection. Nevertheless, the main point ofBlastocystisinfection in children commonly depends on personal hygiene habits and sanitation. However, allele analysis can provide useful information about host specificity and geographic distribution, which can lead to a better understanding ofBlastocystistransmission [42,43]. This study did not show a significant difference in the prevalence ofBlastocystisinfection according to age and sex, which was similar to the finding of the previous studies [44,45].
-Based on the phylogenetic trees of the 17 nucleotide sequences collected from the samples, this protozoan belonged to the ST1, ST2, and ST3 subtypes. Surprisingly, our findings revealed that the nucleotide sequence samples of ST3 were closely correlated with the cattle-derived sequence of the reference sequence (GenBank database). Meanwhile, the nucleotide sequence samples of ST1 were significantly with human-derived sequences in the reference sequence (GenBank database). However, our findings ofBlastocystisST3 might be transmitted from animals to humans, which indicates a zoonotic transmission pattern in this area [23].
-This study is the first regarding the prevalence and subtype distribution ofBlastocystissp. in school-aged children living in the Thai-Myanmar border area, Ratchaburi Province, western Thailand. The prevalence ofBlastocystisinfection was quite low in school-aged children. However, the zoonotic potential is considered inBlastocystisST3 infection. Moreover, the transmission ofBlastocystisinfection between humans to humans should not be disregarded. In this study, no questionnaire was used to assess potential sources of infection. More robust approaches must be carried out to determine possible sources of infection. The risk factors that be studied include the use of unsafe water supplies in the locality, domestic and wild animals in the area, as well as transmission in the households of the school children. Moreover, personal hygiene habits should be improved to promote better health and quality of life among children. Further, the disposal of animal and human wastes should be managed properly.
-The authors would like to thank all students who participated in the study and all teachers for their assistance in the collection. We thank the staff of the Protozoology Department, Faculty of Tropical Medicine, Mahidol University, for excellent laboratory assistance.
-Disclaimer/Publisher’s Note:The statements, opinions and data contained in all publications are solely those of the individual author(s) and contributor(s) and not of MDPI and/or the editor(s). MDPI and/or the editor(s) disclaim responsibility for any injury to people or property resulting from any ideas, methods, instructions or products referred to in the content.
-Conceptualization, A.A. and S.P.; methodology, A.A., S.P., C.S., N.S. and D.A.; investigation, A.A.; software, A.A., A.M. and S.P.; validation, A.A.; formal analysis, A.A., K.K., R.C. and S.P.; writing—original draft preparation, A.A.; writing—review and editing, A.A., D.A., N.S., A.M., C.S., K.K., R.C. and S.P.; funding acquisition, D.A. and S.P.; supervision, S.P. All authors have read and agreed to the published version of the manuscript.
-The study was conducted following the Declaration of Helsinki and approved by the Institutional Review Board of the Faculty of Tropical Medicine, Mahidol University (MUTM 2022-011-01) approved on 15 February 2022 for studies involving humans.
-Informed consent was obtained from all subjects involved in the study.
-Not applicable.
-The authors declare no conflict of interest.
-Map of the study area (modified from Wikipedia, 2010).
-A phylogenic tree of the 17 nucleotide sequences was constructed based on theTamura92+G+I model using the maximum-likelihood algorithm.
-Prevalence ofBlastocystisinfection in school-aged children.
-Accession numbers of positive samples used in the phylogenetic reconstruction.</t>
+          <t>PMID: 7479945
+Abstract: Usher syndrome is a group of diseases with autosomal recessive inheritance, congenital hearing loss, and the development of retinitis pigmentosa, a progressive retinal degeneration characterized by night blindness and visual field loss over several decades. The causes of Usher syndrome are unknown and no animal models have been available for study. Four human gene sites have been reported, suggesting at least four separate forms of Usher syndrome. We report a mouse model of type I Usher syndrome, rd5, whose linkage on mouse chromosome 7 to Hbb and tub has homology to human Usher I reported on human chromosome 11p15. The electroretinogram in homozygous rd5/rd5 mouse is never normal with reduced amplitudes that extinguish by 6 months. Auditory-evoked response testing demonstrates increased hearing thresholds more than control at 3 weeks of about 30 decibels (dB) that worsen to about 45 dB by 6 months.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -692,76 +636,58 @@
     HGNC record ID: HGNC:12406
     Primary gene symbol: TUB
     Official HGNC gene name: TUB bipartite transcription factor
-    Biomedical text context (may include PMID)
+    Biomedical text context
     Task:
-    Determine whether the alias symbol in the given text refers to the gene represented by the provided HGNC record ID.
+    Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
+    as an alternate abbreviation of the official HGNC gene symbol.
+    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
+    The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
+    The text must explicitly link the alias symbol to the official gene name through an expansion 
+    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    Examples:
+    1-
+    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
+    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
+    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
+    Alias gene symbol: A1B
+    Official HGNC gene name: alpha-1-B glycoprotein
+    Primary gene symbol: A1BG
+    2-
+    Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
+    cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Alias gene symbol: ASP
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     Rules:
-    If the text does not support that the alias refers to the provided gene, return:
-    "alias_symbol_represents_primary_gene": "NO"
-    "alternate_abbreviation": ""
-    "evidence": ""
-    If the text does support the gene identity, set "alias_symbol_represents_primary_gene": "YES" and 
-    determine whether the alias symbol in the given text is an alternate abbreviation for the primary gene symbol.
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "NO"
     "evidence": ""
     If the text does support that the alias is an alternate abbreviation, set "alternate_abbreviation": "YES"
-    ALTERNATE ABBREVIATION → alias is expanded to a phrase identically matching the official HGNC gene name
-    ALTERNATE ABBREVIATION — POSITIVE EXAMPLE
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Primary gene symbol: A1BG
     Evidence must be one exact sentence copied verbatim from the text.
     Do not infer relationships or paraphrase evidence.
     Output (Strict):
-    Output only one JSON object. No explanations. No markdown.
+    Output only one JSON object. No markdown.
     {
     "pmid": "",
     "alias_symbol": "",
     "primary_gene_symbol": "",
     "name": "",
-    "alias_symbol_represents_primary_gene": "YES or NO",
     "alternate_abbreviation": "YES or NO",
     "evidence": ""
     }
-PMID: 36612533
-Full Text: Blastocystisis one of the most common enteric protozoa that inhabits the intestinal tract of humans and different animals. Moreover, it has a worldwide geographic distribution. Its main mode of transmission is via the fecal-oral route. At present, 26 subtypes are widely distributed across both humans and animals. The current study aimed to determine the prevalence and subtype distribution ofBlastocystisamong school-aged children living on the Thai-Myanmar border, Ratchaburi province, Thailand. In total, 508 samples were collected from children at six schools. The prevalence ofBlastocystisinfection was amplified and sequenced in the 600 bp barcode region of the small-subunit ribosomal RNA (SSU rRNA). The overall prevalence ofBlastocystisinfection was 3.35% (17/508). ST3 (11/17) was the most predominant subtype, followed by ST1 (5/17) and ST2 (1/17). A phylogenetic tree was constructed based on the Tamura92+G+I model using the maximum-likelihood algorithm. Surprisingly, all sequences of the ST3-positive samples were closely correlated with the cattle-derived sequence. Meanwhile, all sequences of theBlastocystisST1-positive samples were closely correlated with the human-derived sequence. Nevertheless, further studies should be conducted to validate the zoonotic transmission ofBlastocystis. Based on our findings, personal hygiene and sanitation should be improved to promote better health in children in this area.
-Intestinal parasitic infections are one of the main public health issues worldwide, and their incidence is higher in developing than in developed countries [1,2].Blastocystisis a common enteric protozoan causing parasitic intestinal infections among children. Further, it mainly colonizes the gastrointestinal tract, and it is transmitted via the fecal-oral route [3,4]. At present, approximately more than 1 billion humans are infected withBlastocystisworldwide [5]. Its transmission is correlated with several factors, such as poor personal hygiene, consumption of contaminated food, and environmental conditions associated with poor quality of life [6,7,8]. Moreover, close contact with animals due to cultural conditions may causeBlastocystisinfection [9,10,11]. Additionally, school-aged children are at high risk ofBlastocystisinfection due to poor hygiene habits [1,4]. Several studies showed that the prevalence ofBlastocystisinfection varies from 0.7% to 45.2% among school-aged children in Thailand [12,13,14,15]. At present, 26 subtypes ofBlastocystisare widely distributed in both humans and animals. Among them, subtype 3 is most commonly observed in humans [16,17]. The methods used to detectBlastocystisare usually based on microscopy. However, these techniques have low sensitivity and specificity, and assessment using these strategies should be performed by skilled microscopists to validate morphology [18,19,20]. In recent years, polymerase chain reaction (PCR), a molecular biology technique, targets a region of the SSU rRNA genes. Moreover, it has the highest sensitivity and specificity and can identify different subtypes [21,22,23]. However, studies on the incidence and subtypes ofBlastocystisin school-aged children living in the border areas of Thailand are limited. The current study aimed to determine the prevalence and subtype distribution ofBlastocystisisolated from school-aged children living in the Thai-Myanmar border areas, Ratchaburi Province, Thailand.
-This cross-sectional study included children aged 4–12 years from six primary schools in Suan Pheung district, Ratchaburi province, near the Thai-Myanmar border, a natural border in western Thailand (Figure 1). Ratchaburi province is divided into 10 districts. Suan Pheung district, which has important natural resources, is the most popular. The forest covers an area of 1711 km2, or 33% of the provincial area. The area is part of the Tenasserim Hills and the Tanintharyi division of Myanmar. The population in this area have low income and education levels. Most people are agriculture employees and construction laborers and some are unemployed. They commonly consume rainwater, stream water, and water from community wells. Fecal samples were collected from children from HP School, TKL School, RJ School, TMK School, SP School, and BW School, which are located in different sub-districts and are all government primary schools.
-The study protocol was approved by the Ethics Committee of the Faculty of Tropical Medicine, Mahidol University (MUTM: 2022-011-01). All fecal samples were collected from both boys and girls. The participants were commonly from the Kayin, Kayar, and Mon ethnic groups. They were aged between 4–12 years and were in kindergarten and grades 1–3. All participants were instructed to ask permission from their parents, and a written informed consent form was obtained before study participation. Children who were not allowed by their parents to join the research were excluded. In total, 508 fecal samples (n= 270, boys andn= 238, girls) were collected. Moreover, according to the schools, the numbers of samples collected were as follows: 98, TKL; 170, HP; 74, TMK; 96, SP; 47, BW; and 23, RJ. There was no substantial difference in the dates of fecal collection among schools. A single sample was collected from each participant. All participants were instructed to collect fecal samples properly. Clean and labeled plastic containers, toilet tissue paper, and applicator sticks were provided. During transportation, the fecal samples were kept preserved at −20 °C until DNA extraction.
-DNA was extracted from all fecal samples using a commercially available DNA extraction kit (PSP Spin Stool Kit, Stractec Molecular, Berlin, Germany), according to the manufacturer’s instructions. All extracted DNAs from fecal samples were stored at −20 °C until conventional PCR. The primers amplified ~600 bp of the SSU rRNA gene. The primers were as follows: forward primer RD5 5′-ATC TGG TTG ATC CTG CCA GT-3′ and reverse primer BhRDr 5′-GAG CTT TTTA ACT GCA ACA ACG-3′ [23]. The 25 µL reaction in each mixture tube contained 1x PCR buffer, 1.5 mM MgCl2, 0.2 mM dNTPs, 1 µM of each primer, and 2.5 UTaqDNA polymerase (Fermentus, Waltham, MA, USA). The PCR conditions were as follows: 1 cycle denaturing step at 94 °C for 3 min, followed by 35 cycles of annealing step at 59 °C for 1 min, and extension step at 72 °C for 1 min. The last cycle was extended for 5 min at 72 °C. The PCR product and 100bp DNA marker was run on 1.5% agarose gel electrophoresis using 1% tris-acetate-EDTA, which is a running buffer. The gel was stained with Hydra green and visualized under an ultraviolet transilluminator.
-Blastocystis-positive samples were sequenced on an ABI 3730x1 automated DNA sequencer. The nucleotide sequences were aligned and compared with reference sequences available in the GenBank database using BLAST (http://blast.ncbi.nlm.nih.gov/, accessed on 5 May 2022) for subtype identification.The blastocystis18S allele database was tested athttp://pubmlst.org/blastocystis/, accessed on 10 May 2022). All 17 nucleotide sequences and reference sequences (ST1-ST17) were manually edited using BioEdit version 7.2.5 (Ibis Biosciences, Inc., Carlsbad, CA, USA) and multiply aligned using the ClustalW programs. Phylogenetic analysis was performed using MEGA version 7. A phylogenetic tree was constructed using the Tamura92+G+I model with the maximum-likelihood algorithm and was tested with 1000 bootstrap replicates.
-Descriptive analysis was performed to express the percentages of the positive samples ofBlastocystis. The chi-square test was used to compareBlastocystisprevalence according to age and sex. Ap-value of &lt;0.05 was considered statistically significant.
-The prevalence rate ofBlastocystisinfection was 3.35% (17/508) based on the assessment performed using PCR, as shown inTable 1. According to the schools, the prevalence rate was 7.14% (7/98) in TKL, 5.40% (4/74) in TMK, 2.35% (4/170) in HP, 2.13% (1/47) in BW, 1.04% (1/96) in SP, and 0% (0/23%) in RJ.
-The subtype ofBlastocystiswas determined via direct sequencing of the barcode region of the 18S rRNA gene. ST1, ST2, and ST3 were found inBlastocystis-positive fecal samples. ST3 was the predominant subtype (64.71%; 11/17), followed by ST1 (29.41%; 5/17) and ST2 (5.88%; 1/17). TheBlastocystisprevalence was classified according to sex male and female;χ2= 0.096, df= 2,p &gt;0.05) and age ≤6 and &gt;6 years;χ2= 0.145, df= 2,p&gt; 0.05). Results showed that there were no significant differences in theBlastocystisprevalence between sex and age.
-The 17 nucleotide sequences of the barcode region of the SSU rRNA gene were significantly similar (≥98%) to the references ofBlastocystisdeposited in the GenBank databaseTable 2. Results showed that the nucleotide sequence samples belong to the three district subtypes: ST3: TKL25, TKL58, TKL85, TKL95, TKL98, HP83, TMK10, TMK33, TMK69, and BW38; ST1: TKL67, TKL89, HP110, HP161, TMK55, and SP4; and ST2: HP95. The phylogenic tree of the 17 nucleotide sequence samples and the 17 reference sequences in each subtype in the GenBank database was constructed based on the Tamura92+G+I model using the maximum-likelihood algorithm.Proteromonas lacerate(U37108) andKarotomorphaspp. (DQ431242) were classified under the out-group. The sequence ofBlastocystisST1-positive samples was closely correlated with human-derived sequences in the GenBank database. Moreover, the sequence of theBlastocystisST3-positive samples was closely correlated with that of the cattle-derived sequences in the GenBank database, as shown inFigure 2.
-Blastocystisis one of the most common intestinal protozoa that can infect both humans and animals, and it has a worldwide geographic distribution. The current study aimed to assess the prevalence and subtype distribution ofBlastocystisin school-aged children living in the Thai-Myanmar border area. The present study showed a rather low prevalence ofBlastocystisinfection but higher than the study conducted on Thailand’s school children, such as in the Kanchanaburi provinces in the western region of Thailand [24]. It might be different from the method of detection and study population. In Thailand, the prevalence rates ofBlastocystisinfection are 0.7% to 45.2% in school-aged children and the highest infection in young children living in orphan homes in Pathum Thani province [12,13,14,15]. Several studies reported that the prevalence ofBlastocystisinfection was higher in developing countries than in developed countries. Moreover, the prevalence varies from 0.5% to 30% in developed countries, and it is as high as 100% in developing countries [25,26,27,28,29,30].
-The border area in some countries is predominantly rural, people live in poverty, and they lack education. Moreover, its economic development is low [31,32], and the open-defecation behavior of people in this region is attributed to a lack of latrines and water; hence, they are at risk of infection [31,32]. The prevalence rates ofBlastocystisare 37.2% on the Thai-Myanmar border and 6.29% on the China-Myanmar border. The infection is correlated with poor hygiene habits and sanitation in the communities, zoonotic transmission, person-to-person contamination, and consumption of contaminated water [31,32]. However, in this study, the prevalence ofBlastocystisinfection was low. This might be attributed to improvements in common living conditions and easy access to healthcare services, which are attributed to economic growth. Generally, children in this area are not Thai. Most of them are Kayin, Kayar, and Mon. They have access to education and have more opportunities for learning and healthy living. This might explain why the prevalence ofBlastocystisinfection was low.
-Several methods are used for detectingBlastocystisin routine parasitology laboratory examinations, and these include microscopy, xenic in-vitro culture, and molecular biology-based techniques [18,19,20]. Detection is commonly based on microscopy. However, this method has low sensitivity and specificity. It may lead to underdiagnosis and false-positive or false-negative results. The assessment using this strategy should be performed by skilled microscopists to confirm the morphology [18,19,20]. Previous studies have shown that PCR is a rapid and effective method for identifying microorganisms. Further, it can be used for epidemiological studies with a large number of samples [33]. In this study, PCR and the direct sequence technique were applied to detect the subtype ofBlastocystisusing 600 bp of the barcode region. This is the best representative in public databases, and it can be utilized for the analysis of 18S alleles to identify intrasubtype genetic variations [23]. Currently, 26 subtypes ofBlastocystishave been identified in humans and animals [16,34]. ST1-ST4 are the most common subtypes found in humans, and they can occur worldwide [35,36]. This study showed that ST3 was the predominant subtype in boys and girls, followed by ST1 and ST2. This result was similar to that of previous studies in Thailand [35,36] and others in different countries, such as Malaysia [37], Turkey [38], Peru [39], and Italy [40]. Our finding showed 18S alleles ofBlastocystisin each ST, which include allele 4 (ST1), allele 9 (ST2), and alleles 34 and 37 (ST3). Moreover, allele 4 (ST1) is closely correlated with person-to-person transmission [41]. Our result followed that of a previous study on young children from daycare centers because children are less careful about their personal hygiene, leading to more person-to-person transmission [41]. Additionally, allele 9 was most prevalent in both humans and animals, and it might be correlated with zoonotic transmission [42]. Moreover, allele 34 was the predominant allele in non-human primates, such as cattle, thus indicating the possibility of non-host specificity [43]. The parents of most children were agriculture and animal-care workers. Hence, children could have close contact with animals that may cause zoonotic infection. Nevertheless, the main point ofBlastocystisinfection in children commonly depends on personal hygiene habits and sanitation. However, allele analysis can provide useful information about host specificity and geographic distribution, which can lead to a better understanding ofBlastocystistransmission [42,43]. This study did not show a significant difference in the prevalence ofBlastocystisinfection according to age and sex, which was similar to the finding of the previous studies [44,45].
-Based on the phylogenetic trees of the 17 nucleotide sequences collected from the samples, this protozoan belonged to the ST1, ST2, and ST3 subtypes. Surprisingly, our findings revealed that the nucleotide sequence samples of ST3 were closely correlated with the cattle-derived sequence of the reference sequence (GenBank database). Meanwhile, the nucleotide sequence samples of ST1 were significantly with human-derived sequences in the reference sequence (GenBank database). However, our findings ofBlastocystisST3 might be transmitted from animals to humans, which indicates a zoonotic transmission pattern in this area [23].
-This study is the first regarding the prevalence and subtype distribution ofBlastocystissp. in school-aged children living in the Thai-Myanmar border area, Ratchaburi Province, western Thailand. The prevalence ofBlastocystisinfection was quite low in school-aged children. However, the zoonotic potential is considered inBlastocystisST3 infection. Moreover, the transmission ofBlastocystisinfection between humans to humans should not be disregarded. In this study, no questionnaire was used to assess potential sources of infection. More robust approaches must be carried out to determine possible sources of infection. The risk factors that be studied include the use of unsafe water supplies in the locality, domestic and wild animals in the area, as well as transmission in the households of the school children. Moreover, personal hygiene habits should be improved to promote better health and quality of life among children. Further, the disposal of animal and human wastes should be managed properly.
-The authors would like to thank all students who participated in the study and all teachers for their assistance in the collection. We thank the staff of the Protozoology Department, Faculty of Tropical Medicine, Mahidol University, for excellent laboratory assistance.
-Disclaimer/Publisher’s Note:The statements, opinions and data contained in all publications are solely those of the individual author(s) and contributor(s) and not of MDPI and/or the editor(s). MDPI and/or the editor(s) disclaim responsibility for any injury to people or property resulting from any ideas, methods, instructions or products referred to in the content.
-Conceptualization, A.A. and S.P.; methodology, A.A., S.P., C.S., N.S. and D.A.; investigation, A.A.; software, A.A., A.M. and S.P.; validation, A.A.; formal analysis, A.A., K.K., R.C. and S.P.; writing—original draft preparation, A.A.; writing—review and editing, A.A., D.A., N.S., A.M., C.S., K.K., R.C. and S.P.; funding acquisition, D.A. and S.P.; supervision, S.P. All authors have read and agreed to the published version of the manuscript.
-The study was conducted following the Declaration of Helsinki and approved by the Institutional Review Board of the Faculty of Tropical Medicine, Mahidol University (MUTM 2022-011-01) approved on 15 February 2022 for studies involving humans.
-Informed consent was obtained from all subjects involved in the study.
-Not applicable.
-The authors declare no conflict of interest.
-Map of the study area (modified from Wikipedia, 2010).
-A phylogenic tree of the 17 nucleotide sequences was constructed based on theTamura92+G+I model using the maximum-likelihood algorithm.
-Prevalence ofBlastocystisinfection in school-aged children.
-Accession numbers of positive samples used in the phylogenetic reconstruction.</t>
+PMID: 7479945
+Abstract: Usher syndrome is a group of diseases with autosomal recessive inheritance, congenital hearing loss, and the development of retinitis pigmentosa, a progressive retinal degeneration characterized by night blindness and visual field loss over several decades. The causes of Usher syndrome are unknown and no animal models have been available for study. Four human gene sites have been reported, suggesting at least four separate forms of Usher syndrome. We report a mouse model of type I Usher syndrome, rd5, whose linkage on mouse chromosome 7 to Hbb and tub has homology to human Usher I reported on human chromosome 11p15. The electroretinogram in homozygous rd5/rd5 mouse is never normal with reduced amplitudes that extinguish by 6 months. Auditory-evoked response testing demonstrates increased hearing thresholds more than control at 3 weeks of about 30 decibels (dB) that worsen to about 45 dB by 6 months.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>{
-"pmid": "36612533",
+"pmid": "7479945",
 "alias_symbol": "rd5",
 "primary_gene_symbol": "TUB",
 "name": "TUB bipartite transcription factor",
-"alias_symbol_represents_primary_gene": "NO",
-"alternate_abbreviation": "",
+"alternate_abbreviation": "NO",
 "evidence": ""
 }</t>
         </is>
@@ -799,25 +725,27 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>36650547</t>
-        </is>
+      <c r="H3" t="n">
+        <v>9390831</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>mouse phenotype biomarker</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -827,12 +755,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>TUB (MIM #601197), also known as rd5 or RDOB, maps to 11p15.4 and encodes the tubby-bipartite transcription regulator</t>
+          <t>Mice homozygous for a defect of the tub (rd5) gene exhibit cochlear and retinal degeneration combined with obesity, and resemble certain human autosomal recessive sensory deficit syndromes.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -843,71 +771,54 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Retinitis pigmentosa (RP) is the most common type of inherited retinopathy. At least 69 genes for RP have been identified. A significant proportion of RP, however, remains genetically unsolved. In this study, the genetic basis of a Chinese consanguineous family with presumed autosomal recessive retinitis pigmentosa (arRP) was investigated.
-Overall ophthalmic examinations, including funduscopy, decimal best-corrected visual acuity, axial length and electroretinography (ERG) were performed for the family. Genomic DNA from peripheral blood of the proband was subjected to whole exome sequencing. In silico predictions, structural modelling, and minigene assays were conducted to evaluate the pathogenicity of the variant.
-A novel homozygous variant (NM_003320.4: c.1379A &gt; G) in theTUBgene was identified as a candidate pathogenic variant in this parental consanguineous pedigree. This variant co-segregated with the disease in this pedigree and was absent in 118 ethnically matched healthy controls. It’s an extremely rare variant that is neither deposited in population databases (1000 Genomes, ExAC, GnomAD, or Exome Variant Server) nor reported in the literature. Phylogenetic analysis indicated that the Asn residue at codon 460 of TUB is highly conserved across diverse species from tropicalis to humans. It was also completely conserved among the TUB, TULP1, TULP2, and TULP3 family proteins. Multiple bioinformatic algorithms predicted that this variant was deleterious.
-A novel missense variant inTUBwas identified, which was probably the pathogenic basis for arRP in this consanguineous family. This is the first report of a homozygous missense variant inTUBfor RP.
-The online version contains supplementary material available at 10.1186/s12920-023-01430-0.
-Retinitis pigmentosa (RP), a highly heterogenous genetic disorder, is the most common inherited retinopathy induced by progressive loss of photoreceptor cells and subsequent degeneration of the retina. Typical clinical manifestations of RP include night blindness, bone-spicule deposits, gradual loss of central vision, waxy optic disc, and attenuated retinal arteries. The prevalence of RP varied significantly among ethnic groups ranging from 1/1000 to 1/ 5000 worldwide [1–3]. RP can be inherited in classic Mendelian inheritance (including 20–25% autosomal recessive, 15–20% autosomal dominant, and 10–15% X-linked) [2] as well as rarely mitochondrial [4] and digenic [5] inheritance. Although most cases of RP are monogenic, the disease is highly genetically heterogeneous. To date, at least 69 genes have been identified for nonsyndromic RP (including 23 genes for adRP, 44 genes for arRP, and 2 for xlRP) (RetNet,https://sph.uth.edu/retnet, updated October 7, 2022). Generally, broad functions of the identified genes can be classified into five groups: RNA splicing, cellular structure, retinal metabolism, photo-transduction, and tissue development and maintenance [6]. These genes, however, account for no more than 60% of all patients [7,8], and the rest remain genetically unsolved. In China, mutations in about 34 genes have been detected, among which the top seven genes areCYP4V2,RHO,USH2A,RPGR,CRB1,RP2, andCHM, accounting for about two thirds of the RP-related mutations in our Chinese population [9]. Identification of additional genes or novel variants is a prerequisite for genetic counseling, and it’s key to better define the genetic etiology of RP. The remarkable genetic and phenotypic heterogeneity of arRP, however, remains a major obstacle in the identification of pathogenic variants. In addition, some homozygous variants are too rare to be screened in general case–control studies. Whereas pedigrees with hereditary diseases, especially consanguineous pedigrees, are extremely valuable resources for genetic studies of inherited diseases such as arRP.
-TUB(MIM #601197), also known asrd5orRDOB, maps to 11p15.4 and encodes the tubby-bipartite transcription regulator [10,11]. Abundantly expressed in the retina, brain, and cochlea [12–14] with dual localization to the plasma membrane and nucleus [10],TUBhas been implicated in energy balance [15,16], retinal degeneration [12], and neuronal regulation in mice [17]. However, the underlying molecular mechanism remains to be fully elucidated. Previous studies have demonstrated that loss-of-function mutations inTubor Drosophila king tubby(ktub)cause retinal degeneration in both mice and Drosophila [18–21].Mutations inTUBfor retinal-associated diseases in humans, however, are extremely rare. Thus far, only one mutation inTUBfor arRP have been reported in the literature, in which a homozygous frameshift variant resulted in retinal dystrophy, hearing loss, and obesity in a consanguineous UK Caucasian family [12]. Here, we describe a novel rare homozygousTUBvariant (NM_003320.4, c.1379A &gt; G, p.Asn460Ser) in a Chinese consanguineous family with typical arRP. In silico predictions, structural modelling, and experimental studies were conducted to evaluate the pathogenicity of this variant.
-A Chinese parental consanguineous family (living in the remote countryside of Hunan Province) with arRP (Fig.1) and 118 ethnicity and region-matched healthy adults were enrolled by the Department of Ophthalmology of Hunan Provincial People’s Hospital. Overall ophthalmic examinations including funduscopy, decimal best-corrected visual acuity (BCVA), axial length and electroretinography (ERG), were performed by senior ophthalmologists. This study was approved by the Ethics Committee of Hunan Normal University.Fig. 1Pedigree of the arRP family, Fundus and OCT images of the proband.APedigree of the parental consanguineous Chinese family with RP (red arrow indicates the proband of this pedigree, slashed symbols represent deceased members).BFundus images of the proband’s two eyes (R: right, L: left).COptical coherence tomography (OCT) images of the proband (R: right, L: left)
-Pedigree of the arRP family, Fundus and OCT images of the proband.APedigree of the parental consanguineous Chinese family with RP (red arrow indicates the proband of this pedigree, slashed symbols represent deceased members).BFundus images of the proband’s two eyes (R: right, L: left).COptical coherence tomography (OCT) images of the proband (R: right, L: left)
-Genomic DNA from peripheral blood leukocytes of the proband was subjected to WES analysis on Illumina NovaSeq 6000 at the Berry Genomics as described previously [22]. Briefly, data were aligned to hg38/GRCh38 with BWA and the average coverage depth was about 100×. The VeritaTrekker® Variant Detection System, Enliven® Data Annotation, and Interpretation System were used to perform SNP, CNV, indel discovery, and genotyping. All nonsynonymous variants (NSVs) including single nucleotide variants (SNVs), splicing sites, and indels were selected and filtered against the dbSNP137 database, the ExAC, gnomAD, 1000 Genomes phase3, and the MyGenostics local database. The variants with a minor allele frequency (MAF) less than 1% were kept as candidates. Pathogenicity of the mutants were assessed following the guidelines of the American College of Medical Genetics and Genomics (ACMG) [23,24]. Benign or Likely-benign mutations were filtered out.
-Primers (Additional file1: Table S1) used to amplify the fragments harboring candidate variants were designed using Primer3 (https://bioinfo.ut.ee/primer3-0.4.0). Samples of 118 ethnicity and region matched healthy controls were also sequenced to screen variants inTUB.SIFT (Sorting Intolerant from Tolerant,http://sift.jcvi.org), Mutation Taster (http://www.mutationtaster.org), PROVEAN (Protein Variation Effect Analyzer,http://provean.jcvi.org), and CADD_Phre (Combined Annotation Dependent Depletion,http://cadd.gs.washington.edu) were used to evaluate the potential pathogenicity of the variant with default parameters. Novopro (https://www.novopro.cn/tools/protein-hydrophilicity-plot.html) was used to evaluate the hydrophobicity of the mutant TUB protein. The sequence alignment of different species were performed using ClustalW (https://www.ebi.ac.uk/Tools/msa/clustalo). The three dimensional protein model was generated with PyMOL (http://www.schrodinger.com/pymol/) [25].
-The 2240-bp DNA fragments ofTUB(including exons 10–12 and introns 10–11) were amplified from the genomic DNA of the proband or a healthy control with primers as the following:TUB-BamHI-F: 5′- aagcttggtaccgagctcggatccGTCCAACTTGATGGGCACCAAGTTCACT-3′;TUB-XhoI-R: 5′- ttaaacgggccctctagactcgagGGTCATTGCCATGGATGATCTGGAAGTT-3′. After treatment with restriction endonucleases BamHI and XhoI, the amplified fragments were cloned into pMini-CopGFP using the KOD-Plus Neo Kit (TOYOBO CO., OSAKA, JAPAN). The recombinant constructs were confirmed by Sanger sequencing. The wild type (pMini-CopGFP-TUB-WT) and mutant type (pMini-CopGFP-TUB-MT) recombinant constructs were then transiently transfected into two commonly used mammalian cell lines (APRE-19 and 293 T cells) following the protocol provided by the TurboFect kit (Thermo, USA). RT-PCR was performed to obtain the target fragments of humanTUBgene with primers as the following: MiniRT-F: 5’-GGCTAACTAGAGAACCCACTGCTTA-3’;TUB-RT-R: 5’-GGTCATTGCCATGGATGATCTG-3’. The amplified fragments were detected on 1.5% agarose gel and further verified by Sanger sequencing.
-In this five-generation parental consanguineous Chinese pedigree (Fig.1A), the proband (IV:4) and three healthy individuals (IV:5, V: 1, and V: 2) were enrolled in this study. Comprehensive ophthalmic examinations were performed for them. The proband exhibited night blindness and decreased visual acuity since the age of 16, and received a well-defined clinical diagnosis of RP at age 35. The last examination was carried out at age 59 with a BCVA of index/20 cm and 0.25 in the right and left eyes. The axial length was 22.40 mm in the right eye and 23.60 mm in the left eye. Funduscopy displayed spread attenuated arterioles, waxy optic disc, tunnel field, diffused bone-spicule deposition, and atrophy of the choroid in both eyes (Fig.1B). OCT images showed perifoveal retinal thinning in both fundi (Fig.1C). At ages 53 and 59, the proband underwent cataract surgery in the right eye and left eye, respectively. In addition, the proband exhibited no other related disorders nor additional phenotypes such as obesity or hearing deficits as described in other report [12]. The husband and two daughters of the proband were asymptomatic with normal funduscopic observations.
-WES was performed for the proband. After mapping to the human reference genome (hg38), we achieved 3.2G bases with a mean sequencing depth of 100×, among which ≥ 20 × read depth were approximately 98.92%. A total of 53,556 genetic variants including indels and SNPs were detected in the initial WES data of the proband. After exclusion of high-frequency variants in thegnomAD, 1000G phase III, ExAC, and MyGenostics local database, four candidate variants including three heterozygous variants inRAX2, RP1,andPITPNM3,and a homozygous variant inTUB, were remained as suspected pathogenic variants (Additional file1: Table S2). Further co-segregation investigation and genotype–phenotype correlation analysis excluded the pathogenicity of the three heterozygous variants inRAX2, RP1andPITPNM3.A novel homozygous mutation inTUB(c.1379A &gt; G. p.Asn460Ser) remained as the only candidate variant, and no additional causative mutations in all other known RP genes were detected.
-Further Sanger sequencing validated the proband (IV: 4) harbored theTUBvariant in a homozygous state, whereas his husband (IV: 5) was homozygous for the wild type alleles and two unaffected daughters (V: 1, V:2) were heterozygous carriers for the variant (Fig.2). The homozygous variant, based on Sanger sequencing, was verified to co-segregate with the RP phenotype in an autosomal recessive inheritance manner and was excluded from 118 ethnically and regionally matched normal controls. Although the same variant deposited in ClinVar (variation ID: 1,091,773) was interpreted as “likely benign”, we propose that such “likely benign” interpretation is invalid since detailed information about the variant including the variant type, the inheritance pattern, the ethnic group, affected status, or allele origin were not provided. Furthermore, the same variant was also deposited in dbSNP as a SNP (rs189328202) with a frequency of 0.00080, 0.000159 and 0.00005 in 1000G, ExAC, and GnomAD, respectively (Table1). Importantly, the variant was not reported in a homozygous state in all public database (Table1). This novel homozygous variant (c.1379A &gt; G. p.Asn460Ser) inTUBappeared to be extremely rare as it was not reported in the literature either.Fig. 2Co-segragation analysis of the c.1379A &gt; G (p.Asn460SerSer) variant inTUB.ASequences of the homozygous c.1379A &gt; G variant in the proband (IV:4);B,CSequences of the heterozygous carries (V:1, V:2) of the family;DSequences of healthy member (IV:5) of the familyTable 1Allele frequency (G) of c.1379A &gt; G in exon 11 ofTUB(rs189328202) among different population (Released April 9, 2022)Number of Homozygotes (G/G)Number of Heterozygotes (A/G)Ref Allele/Alt AlleleGlobalEast AsianSouth AsianEuropeAmericanAfrican1000G0/50084/5008A = 0.99920A = 0.9960A = 1.000A = 1.000A = 1.000A = 1.000G = 0.00080G = 0.0040G = 0.000G = 0.000G = 0.000G = 0.000GnomAD-Genomes0/1401707/140170A = 0.99995A = 0.9981A = 1.000A = 1.000A = 1.000A = 1.000G = 0.00005G = 0.0019G = 0.000G = 0.000G = 0.000G = 0.000GnomAD-Exomes0/25119449/251194A = 0.999805A = 0.99904A = 0.999993A = 1.000A = 1.000G = 0.000195G = 0.00096G = 0.000007G = 0.000G = 0.000ExAC0/11928819/119288A = 0.999841A = 0.99923A = 1.000A = 1.000A = 1.000G = 0.000159G = 0.00077G = 0.000G = 0.000G = 0.000
-Co-segragation analysis of the c.1379A &gt; G (p.Asn460SerSer) variant inTUB.ASequences of the homozygous c.1379A &gt; G variant in the proband (IV:4);B,CSequences of the heterozygous carries (V:1, V:2) of the family;DSequences of healthy member (IV:5) of the family
-Allele frequency (G) of c.1379A &gt; G in exon 11 ofTUB(rs189328202) among different population (Released April 9, 2022)
-The effect of the non-synonymous variant inTUB(c.1379A &gt; G, p.Asn460Ser) was predicted to be deleterious by PROVEAN with a score of -4.193 (a score ≤ -2.5 is considered deleterious) and damaging by SIFT with a score of 0.035 (a score of 0–0.05 is considered damaging). It was also predicted to be disease-causing by MutationTaster with a score of ~ 1 and damaging by CADD_Phred with a score of 24 (Table2). The hydrophobicity analysis with regard to the changed residue at codon 460 in TUB indicated a lower hydrophilicity than that of the wild type (Fig.3A). Phylogenetic analysis indicated that the Asn residue at codon 460 of TUB is highly conserved across diverse species fromtropicalisto humans (Fig.3B). Further structural modeling (Fig.3C) demonstrated that the changed residue at codon 460 of TUB may contribute to an abnormal TUB conformation. According to the ACMG guidelines [23,24], the c.1379A &gt; G variant inTUBcould be considered as “likely pathogenic”.Table 2Functional predictions of the homozygous mutation of TUB in this studyGeneAccession numberChromosome positionExonVariant TypeVariantMutation TasteraPROVEANb(cutoff = − 2.5)SIFTb(cutoff = 0.05)CADD_Phrec(cutoff = 20)TUBNM_003320.511p15.411Missense Variantc.1379A &gt; G p.Asn460Ser~ 1− 4.190.03524Disease-causingDeleteriousDamagingDamagingahttps://www.mutationtaster.org/bhttp://provean.jcvi.orgchttp://cadd.gs.washington.eduFig. 3Hydrophobicity analysis of the wild and mutant proteins, multiple alignment of the amino acid sequences around Asn460 in different species, and predicted model structures of the human TUB protein.AHydrophobicity analysis performed by Novopro, indicating a slight decrease in hydrophilicity caused by the variant.BMultiple-sequence alignments of TUB around Asn460 among different species, indicating that this variant was highly conserved among species.CPredicted structures of the human TUB protein (residues 289 through 561) using PyMOL. The p.Asn460Ser variant inTUBis indicated with ball-and-stick models. N, asparagine; S, serine
-Functional predictions of the homozygous mutation of TUB in this study
-ahttps://www.mutationtaster.org/
-bhttp://provean.jcvi.org
-chttp://cadd.gs.washington.edu
-Hydrophobicity analysis of the wild and mutant proteins, multiple alignment of the amino acid sequences around Asn460 in different species, and predicted model structures of the human TUB protein.AHydrophobicity analysis performed by Novopro, indicating a slight decrease in hydrophilicity caused by the variant.BMultiple-sequence alignments of TUB around Asn460 among different species, indicating that this variant was highly conserved among species.CPredicted structures of the human TUB protein (residues 289 through 561) using PyMOL. The p.Asn460Ser variant inTUBis indicated with ball-and-stick models. N, asparagine; S, serine
-The minigenes pMini-CopGFP-TUB-WT/MT (Fig.4A) were constructed to explore the splicing effect of this variant. The genomic region spanning from Exon10 to Exon12 ofTUB-WT/TUB-MT were cloned into pMini-CopGFP respectively. RT-PCR analysis showed a single band with the expected size of 460 bp for both WT and MT minigenes in two different cell lines (Fig.4B). And Sanger sequencing confirmed the normal splicing of the minigenes (Exon 10- Exon11- Exon12) (Fig.4C, D), indicating impact of the variant on splicing could be basically ruled out.Fig. 4Minigene assay for the c.1379 A &gt; G variant inTUB.ASchematic illustration of cloned vectors (pMini-CopGFP-TUB minigene), red * indicates the variant site.BElectrophoresis of RT-PCR fragments from APRE-19 cells and 293 T cells (original gel is presented in Additional file1: Fig. S2).CSplicing sequences confirmed by Sanger sequencing.DSchematic diagram shows no effect of theTubvariant (c.1379A &gt; G) on splicing. WT, wild-type; MT, mutant-type
-Minigene assay for the c.1379 A &gt; G variant inTUB.ASchematic illustration of cloned vectors (pMini-CopGFP-TUB minigene), red * indicates the variant site.BElectrophoresis of RT-PCR fragments from APRE-19 cells and 293 T cells (original gel is presented in Additional file1: Fig. S2).CSplicing sequences confirmed by Sanger sequencing.DSchematic diagram shows no effect of theTubvariant (c.1379A &gt; G) on splicing. WT, wild-type; MT, mutant-type
-In the current study, we examined a consanguineous family with arRP from central south China and detected a novel homozygous variant (c.1379 G &gt; A: p.Asn460Ser) inTUB. This variant co-segregated with the disease in an autosomal recessive manner and was absent in 118 ethnically matched healthy controls. This homozygous variant has not been reported in the literature or deposited in existing databases including gnomAD, 1000G phase3, ExAC, or dbSNP, indicating that this variant is rare. Multiple bioinformatic algorithms predicted that this variant was deleterious or damaging. Conservative analysis showed the codon Asn460 fallen within a highly conserved region across diverse species (Fig.3B). Further structural modeling showed that amino acid substitution (Ser) of the variant at residue Asn460 could affect the protein conformation, the binding ability of the tubby domain [26], as well as the solubility and stabilization of the mutant protein [27]. Taken together, these data strongly supported the hypothesis that this novelTUBvariant (c.1379 A &gt; G: p. Asn460Ser) might be the genetic basis of arRP in this Chinese consanguineous family.</t>
+          <t>These authors contributed equally to this work.
+These authors jointly coordinated this work.
+Inherited retinal degeneration (IRD) represents a clinically variable and genetically heterogeneous group of disorders characterized by photoreceptor dysfunction. These diseases typically present with progressive severe vision loss and variable onset, ranging from birth to adulthood. Genomic sequencing has allowed to identify novel IRD-related genes, most of which encode proteins contributing to photoreceptor-cilia biogenesis and/or function. Despite these insights, knowledge gaps hamper a molecular diagnosis in one-third of IRD cases. By exome sequencing in a cohort of molecularly unsolved individuals with IRD, we identified a homozygous splice site variant affecting the transcript processing of TUB, encoding the first member of the Tubby family of bipartite transcription factors, in a sporadic case with retinal dystrophy. A truncating homozygous variant in this gene had previously been reported in a single family with three subjects sharing retinal dystrophy and obesity. The clinical assessment of the present patient documented a slightly increased body mass index and no changes in metabolic markers of obesity, but confirmed the occurrence of retinal detachment. In vitro studies using patient-derived fibroblasts showed the accelerated degradation of the encoded protein and aberrant cilium morphology and biogenesis. These findings definitely link impaired TUB function to retinal dystrophy and provide new data on the clinical characterization of this ultra-rare retinal ciliopathy.
+Inherited retinal degeneration (IRD) occurs in a clinically variable and genetically heterogeneous group of conditions characterized by photoreceptor degeneration and/or dysfunction [1]. The prevalence of monogenic IRD is estimated as 1 in 2000 individuals, affecting more than 2 million people worldwide [2]. This group of disorders typically present with severe vision loss that can be progressive, having an onset ranging from birth to late adulthood. Severe visual impairment affects mobility and independence, posing relevant psychological and economic burdens [3]. In the last ten years, genomic sequencing has allowed the identification of several genes implicated in IRD (for an updated list see the RetNet database,https://sph.uth.edu/retnet/). These genes encode proteins that have different roles in visual function, contributing to key processes in the cells of the pigmented cell layer and neurosensory retina [4,5]. Notably, retinal degeneration is frequently observed in ciliopathies, and a portion of IRD-related genes codifies for proteins involved in biogenesis and the maintenance of photoreceptor primary cilium [6,7,8,9]. Among these genes,TUB[MIM #601197], which encodes the first member of the Tubby family of bipartite transcription factors, has recently reported to be associated with a novel condition characterized by retinal dystrophy and obesity [MIM #616188] [10]. A truncating homozygousTUBvariant [c.1194_1195delAG, p.Arg398Serfs*9] was identified in a single family with three affected members, suggesting loss of function (LoF) as the pathomechanism underlying the disorder. The TUB family of transcription factors counts four members in vertebrates (TUB, TULP1, TULP2 and TULP3), sharing a similar domain organization including a highly conserved C-terminal domain mediating DNA binding and a divergent N-terminal region encompassing the nuclear localization signal and the transcriptional activation domain implicated in protein–protein binding [11]. A conserved region at the N-terminus enables some members of the Tubby family, including TUB, to bind to the ciliary intraflagellar transport A protein (IFTAP) [12]. Similar to the other members of the TULP family, TUB is also implicated in the control of the initiation of phagocytosis, facilitating the removal of apoptotic cells or cellular debris by retinal pigmented epithelium (RPE) cells and macrophages [13]. Since the original report, no other subject carrying biallelicTUBvariants has been described.
+In this study, we report on an additional subject with retinal dystrophy carrying a homozygous LoF variant inTUB. In vitro analyses provide evidence of the disruptive functional impact of the variant onTUBtranscript processing. We also show that the loss of TUB is associated with a defective cilium morphology and biogenesis in the primary patient’s fibroblasts. Our findings confirm the involvement of defective TUB function in retinal dystrophy and define this disorder as a novel ciliopathy.
+The proband is a 35-year-old male, the first child of healthy non-consanguineous parents of European descent (Figure 1). Family history was negative for retinal diseases or other congenital defects. The proband was born at term after an uneventful pregnancy. Length and weight at birth were reported as within the normal range. Apgar score was 8–10. No hearing impairment and/or learning difficulties were documented during the first year of age.
+At 5 years, the subject required consulting ophthalmologists for referring color blindness. A “blonde” aspect of the fundus oculi was observed and reduced full-field flash photopic and scotopic electroretinogram (ERG) responses were recorded. Visual acuity was not investigated at that time. Ophthalmological assessment at 26 years was suggestive of cone-rod dystrophy. Visual acuity was 0.8 Snellen in his right eye (RE) with myopic and astigmatic refractive error (RE: -4.50 dioptre sphere and -1 dioptre cylinder at 20°), and 0.2 Snellen in his left eye (LE) with myopic refractive error (LE: -2.00 dioptre sphere). Goldmann visual field was generally constricted, with reduced sensitivity in the superior central field in the RE and presented peripheral constriction and relative central scotoma in the LE. Light and dark adaptation sensitivity curves showed abnormal thresholds for both cones and rods. No number at the Ishihara charts were recognized. Intraocular pressure was within normal limits. The slit lamp examination biomicroscopy of the anterior segment was normal for cornea, iris and lens appearance. Fundus examination revealed bilateral optic disc pallor, depigmented aspect of the choroidal and retinal structures, diffuse retinal dystrophy with absence of intraretinal pigment dispersion or vitreous abnormalities and arteriolar attenuation. Full-field scotopic and photopic electroretinograms showed reduced a-wave and b-wave amplitude responses and delayed implicit times. Multifocal ERG ring analysis documented reduced response amplitude densities in all examined areas from the foveal center up to 20° of foveal eccentricity in both eyes (LE &gt; RE). After reduced visual field in his LE, a large area of retinoschisis in the infero-temporal sector was observed by fundoscopy, which later progressed, resulting in full retinal detachment of the LE. The subject underwent to pars plana vitrectomy with silicon oil (30% polydimethylsiloxane, PDMS) tamponade. He underwent cataract surgery in his LE and to subsequent vitreo-retinal surgeries for relapsing retinal detachments in same eye (PDMS/perfluorocarbon liquid (PFCL)/PDMS tamponades exchange and intra-operatory laser treatment; PDMS/heavy silicon oil tamponades exchange and intra-operatory laser). One year later, he developed vitreo-retinal proliferation and retinal fibrosis in the LE, and visual acuity was hand motion; therefore, the subject underwent retinotomy and heavy silicon oil/PDMS tamponades exchange.
+At last evaluation (35 years), the subject presented with a good clinical condition. No cognitive deficit nor behavioral issues were observed, and no craniofacial dysmorphism and truncal obesity were noticed. An accurate endocrinological examination was uninformative. Anthropometric assessment displayed a height of 177.5 cm (+0.1 SD), weight of 95.70 kg (+1.6 SD), and OFC 60 cm (+0.2 SD) and BMI of 30.30 Kg/m2(+1.6 SD). Tanner stage was Ph5Pg5, with a testicular volume 20 mL bilaterally. The subject’s visual acuity was 0.8 Snellen in his RE and light perception in his LE. Fundus oculi showed the unmodified condition of RE and diffuse chorio-retinal atrophy in the LE, as for visible vitreo-retinal surgical outcomes. Ultrawide field fundus photography showed macular atrophy in absence of peripheral pigment and confirmed a “blonde” aspect of the retina (Figure 2A). Fundus autofluorescence (FAF) revealed an hypoautoflorescent area in the macula due to RPE atrophy and hyper/hypoautofluorescence mottling in the posterior pole and immediately outside the vascular arcades (Figure 2B). The SD-OCT showed a disruption of the outer retina, including ELM, ellipsoid zone and RPE with outer retinal debris at the level of the RPE in the parafoveal region (Figure 2C). Full-field flash scotopic (Figure 2D) and photopic ERG confirmed reduced a-wave and b-wave amplitude responses and delayed implicit times in the RE. Similarly, multifocal ERG ring analysis, recordable only in the RE, showed the worsening of the response amplitude densities in all examined areas (0–20°) (Figure 2E), as compared to the previous examinations. Similarly, Goldmann visual field in his RE showed progressive constriction of the peripheral isopters and a ring scotoma enclosed between 10–20° of the visual field (Figure 2F); it was not executable, however, in his LE. Color blindness was also confirmed. Neck and abdominal ultrasound assessment did not reveal any abnormality. Measurements of basal hormones by the anterior pituitary, glycaemia and insulin were within the normal range. Basal plasma leptin level was in the low normal range, showing no leptin resistance. During his follow-up, clinical and ophthalmological assessments of other family members (parents and younger brother) were unremarkable.
+Trio-based WES allowed to identify a homozygous splice siteTUBvariant (chr11:8122545G &gt; A, GRCh37.p13; c.1387 + 1G &gt; A,NM_177972.3) as the only clinically and functionally relevant event putatively linked to the disorder (Supplemental Table S1). The variant had previously been annotated in public databases (dbSNP, rs1040410003) with low frequency (gnomAD v3.1, MAF = 0.00001972) at the heterozygous state. It was classified as likely pathogenic (PVS1/PM2/PP5) according to the American College of Medical Genetics and Genomics-Association for Molecular Pathology (ACMG-AMP) criteria (ClinVar: VCV000865971.1) [14]. Sanger sequencing confirmed the homozygosity for the variant in the proband and the heterozygous status in the healthy parents and unaffected sib (Figure 1).
+Since the variant was predicted to affect the exon 11 donor splice site, the total RNA from patient-derived skin primary fibroblasts was used to characterize the impact of the nucleotide change on transcript processing. The cDNA fragment encompassing the relevant exons was amplified, confirming the presence of two aberrantly spliced products (Figure 3A). The two aberrant PCR amplicons were isolated from agarose gel, purified and sequenced via Sanger. The former (500 bp) was derived from skipping of the penultimate exon (exon 11, ENST00000299506.3), resulting in a premature termination codon (i.e., p.Glu406Argfs*4), while the latter (1172 bp) was the result of retention of intron 10, resulting in a TUB protein having a divergent 19-residue-long C-terminus and lacking the last 44 amino acids (p.Pro463Hisfs*19) (Figure 3B).
+In the patient’s skin fibroblasts, the predicted TUBGlu406Argfs*4protein was undetectable by Western blot [WB] analysis, while the TUBPro463Hisfs*19protein was poorly detectable likely due to accelerated degradation (Figure 3C, left panel). Consistently, the endogenous TUBPro463Hisfs*19level was partially rescued by blocking the proteasomal degradation pathway using MG132 (Figure 3C, right panel).
+To investigate the cellular localization of the mutated protein, cytoplasm and nuclear cell fractions were obtained and analyzed by WB. The results demonstrate that both the wild-type (wt) and mutant TUB proteins were almost exclusively localized in the nucleus (Figure 3D). This finding was also confirmed by confocal microscopy analysis that evidenced the nuclear localization of the TUB mutant (Figure 4A).
+Based on the documented role of TUB in early ciliogenesis [15], we assessed the localization of TUB at the cilium, but we failed to observe any consistent co-localization, possibly due to the low diffused levels of the protein in the cytoplasm To investigate the impact of defective TUB function on the morphogenesis of the primary cilium, a confocal analysis on primary fibroblasts was performed using antibodies against ARL13B, which localizes to primary cilia, and pericentrin, a component of the centrosome, which stains the basal body. As shown inFigure 4B, while almost all the control cells showed a primary cilium, 40% of the fibroblasts carrying the homozygous splice site variant inTUBdid not show a primary cilium. Moreover, while no significant difference was observed in ciliary axoneme length between the starved control and mutant cells, a large percentage of the latter showed an abnormal cilium morphology and a poorly defined and disorganized basal body (Figure 4C).
+The loss of TUB function was recently reported to underlie a novel IRD condition based on the identification of homozygosity for a 2 bp deletion (c.1194_1195delAG) causing the premature termination of the protein (p.Arg398Serfs*9) shared by three affected members of a single consanguineous family [10]. While the combination of retinal dystrophy and early onset obesity can be reminiscent of other disorders (e.g., Bardet–Biedl syndrome (MIM#PS209900) and Alstrom syndrome (MIM#203800)), the absence of other clinically relevant feature/sign was suggestive of a previously unreported ciliopathy [10]. In this paper, we report on a second disruptive variant (c.1387 + 1G &gt; A) affectingTUBin a subject with features that overlap with those previously described in the affected members of the original family.
+In the present and previously reported affected individuals, the ocular phenotype associated with defective TUB function is characterized by widespread retinal pigment epithelial (RPE) atrophy, deteriorating vision, the myopic and astigmatic refractive defect, the blonde fundus appearance, the ERG and OCT findings and progression of the disease (Figure 2). Notably, retinal detachment, without vitreous hemorrhage, was invariantly documented in the four individuals with biallelic inactivatingTUBvariants, suggesting that this feature likely represent a common finding in the disorder.
+Early onset obesity had previously been considered a major feature of the TUB-related condition [10], even though only two of three affected sibs were found obese (BMI &gt; 30), and the glycemic and lipid profiles in one of affected sibs were found within the normal range. The finding of obesity in the apparently healthy father (heterozygous carrier) suggests a possible co-occurring genetic event contributing to obesity in the family. In the present report, the clinical assessment of the affected individual documented increased weight (95.7 kg, +1.6 SD) and BMI (30.3, +1.6 SD), thus indicating overweight, in absence of other signs of obesity. Although evidence suggests that a defective TUB function may result in disturbances in insulin and leptin activity and obesity in mice [16,17,18,19], based on the collected findings, the relevance of TUB in human obesity requires further study. To assess whether TUB LoF could impact on hypothalamic pathways, food intake and adiposity, the metabolic profile of the affected individual was investigated. Accurate endocrinological examination did not reveal any abnormality, and the measurements of basal hormones by the anterior pituitary, glycaemia, insulin and leptin were within the normal range, thus ruling out insulin or leptin resistance. Consistently, instrumental investigations (X-ray and ultrasound analyses) documented no sign of glycogen accumulation in the internal organs. Consistently, the absence of significant changes in lipid storage was demonstrated by thin-layer chromatography (HPTLC) analysis in proband-derived fibroblast (Figure S1), allowing to confirm an apparently normal endocrine–metabolic profile in the affected individual. Of note, the Tubby protein has been involved in cochlear degeneration [20,21]. Based on this functional link, we evaluated the occurrence of hearing problems and cochlear degeneration, which were not observed.
+The homozygousTUBvariant was predicted to affect transcript processing, causing the skipping of exon 11 and intron retention, resulting in a frameshift with the premature termination of the TUB protein. mRNA analysis in proband-derived fibroblasts confirmed a disruptive impact of the splice site change documenting two aberrantly processed transcripts predicted to encode a 406-residue-long protein (p.Glu406Argfs*4) that probably is not able to proceed in protein synthesis, and a 481-residue-long protein (p.Pro463Hisfs*19) characterized by a divergent C-terminus characterized by accelerated degradation (Figure 3B). These findings confirm LoF as the pathomechanism underlying this disorder.
+Primary cilia are microtubule-based organelles that extend from the apical surface of the majority of mammalian cells. Cilia act as “cellular antennae”, receiving different inputs from the extracellular environment and transducing signals in response to stimuli [22]. A complex process required for proper cilia biogenesis function is the intraflagellar transport, which is required for assembling cilia and trafficking within primary cilia [23]. In this context, IFT-A has historically been believed to mediate retrograde intraflagellar transport inside the cilia and an IFT-A-binding domain at the TUB N-terminus has been demonstrated recently [24]. Moreover, co-localization between TUB and rootletin, the major structural component of the ciliary rootlet, has been observed in human retinal photoreceptors [10]. The use of a more informative in vitro model (e.g., induced pluripotent-stem-cell-derived retinal-pigment epithelium cells) and experimental strategies (e.g., siRNA-mediated TUB silencing) is required to appreciate more accurately the functional relevance of TUB in an appropriate cellular context.
+In summary, we confirm the link between TUB LoF and a new condition of human retinal ciliopathy and provide evidence of an altered cilium morphology/biogenesis in patient-derived fibroblasts. In fact, these cells displayed a reduced number of cilia when compared to the control cells, with a poorly defined and disorganized basal body structure, which are expected to prevent normal protein trafficking along the cilium. While these findings could explain the degeneration of photoreceptors characterizing this disorder, a relatively overall mild presentation has been associated with mutations in this gene. Multiple factors might contribute to this picture. First, the functional relevance of TUB in the context of ciliogenesis and cilium function might vary in different cell lineages. Second, functional compensation exerted by other related proteins might contribute to buffer the severity of the endophenotype. Third, specific cell lineages (e.g., rod and cone cells) might be particularly sensitive to TUB LoF. The collection of additional patients with biallelic variants in the gene will allow a more accurate characterization of the clinical spectrum associated with TUB LoF. Based on these considerations, TUB loss of function could be considered as responsible for a novel form of isolated retinal ciliopathy.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Retinitis pigmentosa (RP) is the most common type of inherited retinopathy. At least 69 genes for RP have been identified. A significant proportion of RP, however, remains genetically unsolved. In this study, the genetic basis of a Chinese consanguineous family with presumed autosomal recessive retinitis pigmentosa (arRP) was investigated.
-Overall ophthalmic examinations, including funduscopy, decimal best-corrected visual acuity, axial length and electroretinography (ERG) were performed for the family. Genomic DNA from peripheral blood of the proband was subjected to whole exome sequencing. In silico predictions, structural modelling, and minigene assays were conducted to evaluate the pathogenicity of the variant.
-A novel homozygous variant (NM_003320.4: c.1379A &gt; G) in the TUB gene was identified as a candidate pathogenic variant in this parental consanguineous pedigree. This variant co-segregated with the disease in this pedigree and was absent in 118 ethnically matched healthy controls. It's an extremely rare variant that is neither deposited in population databases (1000 Genomes, ExAC, GnomAD, or Exome Variant Server) nor reported in the literature. Phylogenetic analysis indicated that the Asn residue at codon 460 of TUB is highly conserved across diverse species from tropicalis to humans. It was also completely conserved among the TUB, TULP1, TULP2, and TULP3 family proteins. Multiple bioinformatic algorithms predicted that this variant was deleterious.
-A novel missense variant in TUB was identified, which was probably the pathogenic basis for arRP in this consanguineous family. This is the first report of a homozygous missense variant in TUB for RP.</t>
+          <t>Mice homozygous for a defect of the tub (rd5) gene exhibit cochlear and retinal degeneration combined with obesity, and resemble certain human autosomal recessive sensory deficit syndromes. To establish the progressive nature of sensory cell loss associated with the tub gene, and to differentiate tub-related losses from those associated with the C57 background on which tub arose, we evaluated cochleas and retinas from tub/tub, tub/+, and +/+ mice, aged 2 weeks to 1 year by light and electron microscopy. Cochleas from mice of all three genotypes show progressive inner (IHC) and outer hair cell (OHC) loss. Relative to tub/+ and +/+ animals, however, tub homozygotes show accelerated OHC loss, affecting the extreme cochlear base (hook region) by 1 month, and the apex by 6 months. IHC loss in tub/tub animals is accelerated in the basal half of the cochlea, affecting the hook region by 6 months. Spiral ganglion cell losses were observed only in tub/tub mice, and only in the cochlear base. Retinas of tub/tub mice are abnormal at maturity, exhibiting shortened photoreceptor outer segments by 2 weeks, and progressive photoreceptor loss thereafter. Because the tub mutation causes degeneration of sensory cells in the ear and eye but has no other neurological effects, tubby mice hold unique promise for the study of human syndromic sensory loss.</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>PMID: 36650547
-Full Text: Retinitis pigmentosa (RP) is the most common type of inherited retinopathy. At least 69 genes for RP have been identified. A significant proportion of RP, however, remains genetically unsolved. In this study, the genetic basis of a Chinese consanguineous family with presumed autosomal recessive retinitis pigmentosa (arRP) was investigated.
-Overall ophthalmic examinations, including funduscopy, decimal best-corrected visual acuity, axial length and electroretinography (ERG) were performed for the family. Genomic DNA from peripheral blood of the proband was subjected to whole exome sequencing. In silico predictions, structural modelling, and minigene assays were conducted to evaluate the pathogenicity of the variant.
-A novel homozygous variant (NM_003320.4: c.1379A &gt; G) in theTUBgene was identified as a candidate pathogenic variant in this parental consanguineous pedigree. This variant co-segregated with the disease in this pedigree and was absent in 118 ethnically matched healthy controls. It’s an extremely rare variant that is neither deposited in population databases (1000 Genomes, ExAC, GnomAD, or Exome Variant Server) nor reported in the literature. Phylogenetic analysis indicated that the Asn residue at codon 460 of TUB is highly conserved across diverse species from tropicalis to humans. It was also completely conserved among the TUB, TULP1, TULP2, and TULP3 family proteins. Multiple bioinformatic algorithms predicted that this variant was deleterious.
-A novel missense variant inTUBwas identified, which was probably the pathogenic basis for arRP in this consanguineous family. This is the first report of a homozygous missense variant inTUBfor RP.
-The online version contains supplementary material available at 10.1186/s12920-023-01430-0.
-Retinitis pigmentosa (RP), a highly heterogenous genetic disorder, is the most common inherited retinopathy induced by progressive loss of photoreceptor cells and subsequent degeneration of the retina. Typical clinical manifestations of RP include night blindness, bone-spicule deposits, gradual loss of central vision, waxy optic disc, and attenuated retinal arteries. The prevalence of RP varied significantly among ethnic groups ranging from 1/1000 to 1/ 5000 worldwide [1–3]. RP can be inherited in classic Mendelian inheritance (including 20–25% autosomal recessive, 15–20% autosomal dominant, and 10–15% X-linked) [2] as well as rarely mitochondrial [4] and digenic [5] inheritance. Although most cases of RP are monogenic, the disease is highly genetically heterogeneous. To date, at least 69 genes have been identified for nonsyndromic RP (including 23 genes for adRP, 44 genes for arRP, and 2 for xlRP) (RetNet,https://sph.uth.edu/retnet, updated October 7, 2022). Generally, broad functions of the identified genes can be classified into five groups: RNA splicing, cellular structure, retinal metabolism, photo-transduction, and tissue development and maintenance [6]. These genes, however, account for no more than 60% of all patients [7,8], and the rest remain genetically unsolved. In China, mutations in about 34 genes have been detected, among which the top seven genes areCYP4V2,RHO,USH2A,RPGR,CRB1,RP2, andCHM, accounting for about two thirds of the RP-related mutations in our Chinese population [9]. Identification of additional genes or novel variants is a prerequisite for genetic counseling, and it’s key to better define the genetic etiology of RP. The remarkable genetic and phenotypic heterogeneity of arRP, however, remains a major obstacle in the identification of pathogenic variants. In addition, some homozygous variants are too rare to be screened in general case–control studies. Whereas pedigrees with hereditary diseases, especially consanguineous pedigrees, are extremely valuable resources for genetic studies of inherited diseases such as arRP.
-TUB(MIM #601197), also known asrd5orRDOB, maps to 11p15.4 and encodes the tubby-bipartite transcription regulator [10,11]. Abundantly expressed in the retina, brain, and cochlea [12–14] with dual localization to the plasma membrane and nucleus [10],TUBhas been implicated in energy balance [15,16], retinal degeneration [12], and neuronal regulation in mice [17]. However, the underlying molecular mechanism remains to be fully elucidated. Previous studies have demonstrated that loss-of-function mutations inTubor Drosophila king tubby(ktub)cause retinal degeneration in both mice and Drosophila [18–21].Mutations inTUBfor retinal-associated diseases in humans, however, are extremely rare. Thus far, only one mutation inTUBfor arRP have been reported in the literature, in which a homozygous frameshift variant resulted in retinal dystrophy, hearing loss, and obesity in a consanguineous UK Caucasian family [12]. Here, we describe a novel rare homozygousTUBvariant (NM_003320.4, c.1379A &gt; G, p.Asn460Ser) in a Chinese consanguineous family with typical arRP. In silico predictions, structural modelling, and experimental studies were conducted to evaluate the pathogenicity of this variant.
-A Chinese parental consanguineous family (living in the remote countryside of Hunan Province) with arRP (Fig.1) and 118 ethnicity and region-matched healthy adults were enrolled by the Department of Ophthalmology of Hunan Provincial People’s Hospital. Overall ophthalmic examinations including funduscopy, decimal best-corrected visual acuity (BCVA), axial length and electroretinography (ERG), were performed by senior ophthalmologists. This study was approved by the Ethics Committee of Hunan Normal University.Fig. 1Pedigree of the arRP family, Fundus and OCT images of the proband.APedigree of the parental consanguineous Chinese family with RP (red arrow indicates the proband of this pedigree, slashed symbols represent deceased members).BFundus images of the proband’s two eyes (R: right, L: left).COptical coherence tomography (OCT) images of the proband (R: right, L: left)
-Pedigree of the arRP family, Fundus and OCT images of the proband.APedigree of the parental consanguineous Chinese family with RP (red arrow indicates the proband of this pedigree, slashed symbols represent deceased members).BFundus images of the proband’s two eyes (R: right, L: left).COptical coherence tomography (OCT) images of the proband (R: right, L: left)
-Genomic DNA from peripheral blood leukocytes of the proband was subjected to WES analysis on Illumina NovaSeq 6000 at the Berry Genomics as described previously [22]. Briefly, data were aligned to hg38/GRCh38 with BWA and the average coverage depth was about 100×. The VeritaTrekker® Variant Detection System, Enliven® Data Annotation, and Interpretation System were used to perform SNP, CNV, indel discovery, and genotyping. All nonsynonymous variants (NSVs) including single nucleotide variants (SNVs), splicing sites, and indels were selected and filtered against the dbSNP137 database, the ExAC, gnomAD, 1000 Genomes phase3, and the MyGenostics local database. The variants with a minor allele frequency (MAF) less than 1% were kept as candidates. Pathogenicity of the mutants were assessed following the guidelines of the American College of Medical Genetics and Genomics (ACMG) [23,24]. Benign or Likely-benign mutations were filtered out.
-Primers (Additional file1: Table S1) used to amplify the fragments harboring candidate variants were designed using Primer3 (https://bioinfo.ut.ee/primer3-0.4.0). Samples of 118 ethnicity and region matched healthy controls were also sequenced to screen variants inTUB.SIFT (Sorting Intolerant from Tolerant,http://sift.jcvi.org), Mutation Taster (http://www.mutationtaster.org), PROVEAN (Protein Variation Effect Analyzer,http://provean.jcvi.org), and CADD_Phre (Combined Annotation Dependent Depletion,http://cadd.gs.washington.edu) were used to evaluate the potential pathogenicity of the variant with default parameters. Novopro (https://www.novopro.cn/tools/protein-hydrophilicity-plot.html) was used to evaluate the hydrophobicity of the mutant TUB protein. The sequence alignment of different species were performed using ClustalW (https://www.ebi.ac.uk/Tools/msa/clustalo). The three dimensional protein model was generated with PyMOL (http://www.schrodinger.com/pymol/) [25].
-The 2240-bp DNA fragments ofTUB(including exons 10–12 and introns 10–11) were amplified from the genomic DNA of the proband or a healthy control with primers as the following:TUB-BamHI-F: 5′- aagcttggtaccgagctcggatccGTCCAACTTGATGGGCACCAAGTTCACT-3′;TUB-XhoI-R: 5′- ttaaacgggccctctagactcgagGGTCATTGCCATGGATGATCTGGAAGTT-3′. After treatment with restriction endonucleases BamHI and XhoI, the amplified fragments were cloned into pMini-CopGFP using the KOD-Plus Neo Kit (TOYOBO CO., OSAKA, JAPAN). The recombinant constructs were confirmed by Sanger sequencing. The wild type (pMini-CopGFP-TUB-WT) and mutant type (pMini-CopGFP-TUB-MT) recombinant constructs were then transiently transfected into two commonly used mammalian cell lines (APRE-19 and 293 T cells) following the protocol provided by the TurboFect kit (Thermo, USA). RT-PCR was performed to obtain the target fragments of humanTUBgene with primers as the following: MiniRT-F: 5’-GGCTAACTAGAGAACCCACTGCTTA-3’;TUB-RT-R: 5’-GGTCATTGCCATGGATGATCTG-3’. The amplified fragments were detected on 1.5% agarose gel and further verified by Sanger sequencing.
-In this five-generation parental consanguineous Chinese pedigree (Fig.1A), the proband (IV:4) and three healthy individuals (IV:5, V: 1, and V: 2) were enrolled in this study. Comprehensive ophthalmic examinations were performed for them. The proband exhibited night blindness and decreased visual acuity since the age of 16, and received a well-defined clinical diagnosis of RP at age 35. The last examination was carried out at age 59 with a BCVA of index/20 cm and 0.25 in the right and left eyes. The axial length was 22.40 mm in the right eye and 23.60 mm in the left eye. Funduscopy displayed spread attenuated arterioles, waxy optic disc, tunnel field, diffused bone-spicule deposition, and atrophy of the choroid in both eyes (Fig.1B). OCT images showed perifoveal retinal thinning in both fundi (Fig.1C). At ages 53 and 59, the proband underwent cataract surgery in the right eye and left eye, respectively. In addition, the proband exhibited no other related disorders nor additional phenotypes such as obesity or hearing deficits as described in other report [12]. The husband and two daughters of the proband were asymptomatic with normal funduscopic observations.
-WES was performed for the proband. After mapping to the human reference genome (hg38), we achieved 3.2G bases with a mean sequencing depth of 100×, among which ≥ 20 × read depth were approximately 98.92%. A total of 53,556 genetic variants including indels and SNPs were detected in the initial WES data of the proband. After exclusion of high-frequency variants in thegnomAD, 1000G phase III, ExAC, and MyGenostics local database, four candidate variants including three heterozygous variants inRAX2, RP1,andPITPNM3,and a homozygous variant inTUB, were remained as suspected pathogenic variants (Additional file1: Table S2). Further co-segregation investigation and genotype–phenotype correlation analysis excluded the pathogenicity of the three heterozygous variants inRAX2, RP1andPITPNM3.A novel homozygous mutation inTUB(c.1379A &gt; G. p.Asn460Ser) remained as the only candidate variant, and no additional causative mutations in all other known RP genes were detected.
-Further Sanger sequencing validated the proband (IV: 4) harbored theTUBvariant in a homozygous state, whereas his husband (IV: 5) was homozygous for the wild type alleles and two unaffected daughters (V: 1, V:2) were heterozygous carriers for the variant (Fig.2). The homozygous variant, based on Sanger sequencing, was verified to co-segregate with the RP phenotype in an autosomal recessive inheritance manner and was excluded from 118 ethnically and regionally matched normal controls. Although the same variant deposited in ClinVar (variation ID: 1,091,773) was interpreted as “likely benign”, we propose that such “likely benign” interpretation is invalid since detailed information about the variant including the variant type, the inheritance pattern, the ethnic group, affected status, or allele origin were not provided. Furthermore, the same variant was also deposited in dbSNP as a SNP (rs189328202) with a frequency of 0.00080, 0.000159 and 0.00005 in 1000G, ExAC, and GnomAD, respectively (Table1). Importantly, the variant was not reported in a homozygous state in all public database (Table1). This novel homozygous variant (c.1379A &gt; G. p.Asn460Ser) inTUBappeared to be extremely rare as it was not reported in the literature either.Fig. 2Co-segragation analysis of the c.1379A &gt; G (p.Asn460SerSer) variant inTUB.ASequences of the homozygous c.1379A &gt; G variant in the proband (IV:4);B,CSequences of the heterozygous carries (V:1, V:2) of the family;DSequences of healthy member (IV:5) of the familyTable 1Allele frequency (G) of c.1379A &gt; G in exon 11 ofTUB(rs189328202) among different population (Released April 9, 2022)Number of Homozygotes (G/G)Number of Heterozygotes (A/G)Ref Allele/Alt AlleleGlobalEast AsianSouth AsianEuropeAmericanAfrican1000G0/50084/5008A = 0.99920A = 0.9960A = 1.000A = 1.000A = 1.000A = 1.000G = 0.00080G = 0.0040G = 0.000G = 0.000G = 0.000G = 0.000GnomAD-Genomes0/1401707/140170A = 0.99995A = 0.9981A = 1.000A = 1.000A = 1.000A = 1.000G = 0.00005G = 0.0019G = 0.000G = 0.000G = 0.000G = 0.000GnomAD-Exomes0/25119449/251194A = 0.999805A = 0.99904A = 0.999993A = 1.000A = 1.000G = 0.000195G = 0.00096G = 0.000007G = 0.000G = 0.000ExAC0/11928819/119288A = 0.999841A = 0.99923A = 1.000A = 1.000A = 1.000G = 0.000159G = 0.00077G = 0.000G = 0.000G = 0.000
-Co-segragation analysis of the c.1379A &gt; G (p.Asn460SerSer) variant inTUB.ASequences of the homozygous c.1379A &gt; G variant in the proband (IV:4);B,CSequences of the heterozygous carries (V:1, V:2) of the family;DSequences of healthy member (IV:5) of the family
-Allele frequency (G) of c.1379A &gt; G in exon 11 ofTUB(rs189328202) among different population (Released April 9, 2022)
-The effect of the non-synonymous variant inTUB(c.1379A &gt; G, p.Asn460Ser) was predicted to be deleterious by PROVEAN with a score of -4.193 (a score ≤ -2.5 is considered deleterious) and damaging by SIFT with a score of 0.035 (a score of 0–0.05 is considered damaging). It was also predicted to be disease-causing by MutationTaster with a score of ~ 1 and damaging by CADD_Phred with a score of 24 (Table2). The hydrophobicity analysis with regard to the changed residue at codon 460 in TUB indicated a lower hydrophilicity than that of the wild type (Fig.3A). Phylogenetic analysis indicated that the Asn residue at codon 460 of TUB is highly conserved across diverse species fromtropicalisto humans (Fig.3B). Further structural modeling (Fig.3C) demonstrated that the changed residue at codon 460 of TUB may contribute to an abnormal TUB conformation. According to the ACMG guidelines [23,24], the c.1379A &gt; G variant inTUBcould be considered as “likely pathogenic”.Table 2Functional predictions of the homozygous mutation of TUB in this studyGeneAccession numberChromosome positionExonVariant TypeVariantMutation TasteraPROVEANb(cutoff = − 2.5)SIFTb(cutoff = 0.05)CADD_Phrec(cutoff = 20)TUBNM_003320.511p15.411Missense Variantc.1379A &gt; G p.Asn460Ser~ 1− 4.190.03524Disease-causingDeleteriousDamagingDamagingahttps://www.mutationtaster.org/bhttp://provean.jcvi.orgchttp://cadd.gs.washington.eduFig. 3Hydrophobicity analysis of the wild and mutant proteins, multiple alignment of the amino acid sequences around Asn460 in different species, and predicted model structures of the human TUB protein.AHydrophobicity analysis performed by Novopro, indicating a slight decrease in hydrophilicity caused by the variant.BMultiple-sequence alignments of TUB around Asn460 among different species, indicating that this variant was highly conserved among species.CPredicted structures of the human TUB protein (residues 289 through 561) using PyMOL. The p.Asn460Ser variant inTUBis indicated with ball-and-stick models. N, asparagine; S, serine
-Functional predictions of the homozygous mutation of TUB in this study
-ahttps://www.mutationtaster.org/
-bhttp://provean.jcvi.org
-chttp://cadd.gs.washington.edu
-Hydrophobicity analysis of the wild and mutant proteins, multiple alignment of the amino acid sequences around Asn460 in different species, and predicted model structures of the human TUB protein.AHydrophobicity analysis performed by Novopro, indicating a slight decrease in hydrophilicity caused by the variant.BMultiple-sequence alignments of TUB around Asn460 among different species, indicating that this variant was highly conserved among species.CPredicted structures of the human TUB protein (residues 289 through 561) using PyMOL. The p.Asn460Ser variant inTUBis indicated with ball-and-stick models. N, asparagine; S, serine
-The minigenes pMini-CopGFP-TUB-WT/MT (Fig.4A) were constructed to explore the splicing effect of this variant. The genomic region spanning from Exon10 to Exon12 ofTUB-WT/TUB-MT were cloned into pMini-CopGFP respectively. RT-PCR analysis showed a single band with the expected size of 460 bp for both WT and MT minigenes in two different cell lines (Fig.4B). And Sanger sequencing confirmed the normal splicing of the minigenes (Exon 10- Exon11- Exon12) (Fig.4C, D), indicating impact of the variant on splicing could be basically ruled out.Fig. 4Minigene assay for the c.1379 A &gt; G variant inTUB.ASchematic illustration of cloned vectors (pMini-CopGFP-TUB minigene), red * indicates the variant site.BElectrophoresis of RT-PCR fragments from APRE-19 cells and 293 T cells (original gel is presented in Additional file1: Fig. S2).CSplicing sequences confirmed by Sanger sequencing.DSchematic diagram shows no effect of theTubvariant (c.1379A &gt; G) on splicing. WT, wild-type; MT, mutant-type
-Minigene assay for the c.1379 A &gt; G variant inTUB.ASchematic illustration of cloned vectors (pMini-CopGFP-TUB minigene), red * indicates the variant site.BElectrophoresis of RT-PCR fragments from APRE-19 cells and 293 T cells (original gel is presented in Additional file1: Fig. S2).CSplicing sequences confirmed by Sanger sequencing.DSchematic diagram shows no effect of theTubvariant (c.1379A &gt; G) on splicing. WT, wild-type; MT, mutant-type
-In the current study, we examined a consanguineous family with arRP from central south China and detected a novel homozygous variant (c.1379 G &gt; A: p.Asn460Ser) inTUB. This variant co-segregated with the disease in an autosomal recessive manner and was absent in 118 ethnically matched healthy controls. This homozygous variant has not been reported in the literature or deposited in existing databases including gnomAD, 1000G phase3, ExAC, or dbSNP, indicating that this variant is rare. Multiple bioinformatic algorithms predicted that this variant was deleterious or damaging. Conservative analysis showed the codon Asn460 fallen within a highly conserved region across diverse species (Fig.3B). Further structural modeling showed that amino acid substitution (Ser) of the variant at residue Asn460 could affect the protein conformation, the binding ability of the tubby domain [26], as well as the solubility and stabilization of the mutant protein [27]. Taken together, these data strongly supported the hypothesis that this novelTUBvariant (c.1379 A &gt; G: p. Asn460Ser) might be the genetic basis of arRP in this Chinese consanguineous family.</t>
+          <t>PMID: 9390831
+Full Text: These authors contributed equally to this work.
+These authors jointly coordinated this work.
+Inherited retinal degeneration (IRD) represents a clinically variable and genetically heterogeneous group of disorders characterized by photoreceptor dysfunction. These diseases typically present with progressive severe vision loss and variable onset, ranging from birth to adulthood. Genomic sequencing has allowed to identify novel IRD-related genes, most of which encode proteins contributing to photoreceptor-cilia biogenesis and/or function. Despite these insights, knowledge gaps hamper a molecular diagnosis in one-third of IRD cases. By exome sequencing in a cohort of molecularly unsolved individuals with IRD, we identified a homozygous splice site variant affecting the transcript processing of TUB, encoding the first member of the Tubby family of bipartite transcription factors, in a sporadic case with retinal dystrophy. A truncating homozygous variant in this gene had previously been reported in a single family with three subjects sharing retinal dystrophy and obesity. The clinical assessment of the present patient documented a slightly increased body mass index and no changes in metabolic markers of obesity, but confirmed the occurrence of retinal detachment. In vitro studies using patient-derived fibroblasts showed the accelerated degradation of the encoded protein and aberrant cilium morphology and biogenesis. These findings definitely link impaired TUB function to retinal dystrophy and provide new data on the clinical characterization of this ultra-rare retinal ciliopathy.
+Inherited retinal degeneration (IRD) occurs in a clinically variable and genetically heterogeneous group of conditions characterized by photoreceptor degeneration and/or dysfunction [1]. The prevalence of monogenic IRD is estimated as 1 in 2000 individuals, affecting more than 2 million people worldwide [2]. This group of disorders typically present with severe vision loss that can be progressive, having an onset ranging from birth to late adulthood. Severe visual impairment affects mobility and independence, posing relevant psychological and economic burdens [3]. In the last ten years, genomic sequencing has allowed the identification of several genes implicated in IRD (for an updated list see the RetNet database,https://sph.uth.edu/retnet/). These genes encode proteins that have different roles in visual function, contributing to key processes in the cells of the pigmented cell layer and neurosensory retina [4,5]. Notably, retinal degeneration is frequently observed in ciliopathies, and a portion of IRD-related genes codifies for proteins involved in biogenesis and the maintenance of photoreceptor primary cilium [6,7,8,9]. Among these genes,TUB[MIM #601197], which encodes the first member of the Tubby family of bipartite transcription factors, has recently reported to be associated with a novel condition characterized by retinal dystrophy and obesity [MIM #616188] [10]. A truncating homozygousTUBvariant [c.1194_1195delAG, p.Arg398Serfs*9] was identified in a single family with three affected members, suggesting loss of function (LoF) as the pathomechanism underlying the disorder. The TUB family of transcription factors counts four members in vertebrates (TUB, TULP1, TULP2 and TULP3), sharing a similar domain organization including a highly conserved C-terminal domain mediating DNA binding and a divergent N-terminal region encompassing the nuclear localization signal and the transcriptional activation domain implicated in protein–protein binding [11]. A conserved region at the N-terminus enables some members of the Tubby family, including TUB, to bind to the ciliary intraflagellar transport A protein (IFTAP) [12]. Similar to the other members of the TULP family, TUB is also implicated in the control of the initiation of phagocytosis, facilitating the removal of apoptotic cells or cellular debris by retinal pigmented epithelium (RPE) cells and macrophages [13]. Since the original report, no other subject carrying biallelicTUBvariants has been described.
+In this study, we report on an additional subject with retinal dystrophy carrying a homozygous LoF variant inTUB. In vitro analyses provide evidence of the disruptive functional impact of the variant onTUBtranscript processing. We also show that the loss of TUB is associated with a defective cilium morphology and biogenesis in the primary patient’s fibroblasts. Our findings confirm the involvement of defective TUB function in retinal dystrophy and define this disorder as a novel ciliopathy.
+The proband is a 35-year-old male, the first child of healthy non-consanguineous parents of European descent (Figure 1). Family history was negative for retinal diseases or other congenital defects. The proband was born at term after an uneventful pregnancy. Length and weight at birth were reported as within the normal range. Apgar score was 8–10. No hearing impairment and/or learning difficulties were documented during the first year of age.
+At 5 years, the subject required consulting ophthalmologists for referring color blindness. A “blonde” aspect of the fundus oculi was observed and reduced full-field flash photopic and scotopic electroretinogram (ERG) responses were recorded. Visual acuity was not investigated at that time. Ophthalmological assessment at 26 years was suggestive of cone-rod dystrophy. Visual acuity was 0.8 Snellen in his right eye (RE) with myopic and astigmatic refractive error (RE: -4.50 dioptre sphere and -1 dioptre cylinder at 20°), and 0.2 Snellen in his left eye (LE) with myopic refractive error (LE: -2.00 dioptre sphere). Goldmann visual field was generally constricted, with reduced sensitivity in the superior central field in the RE and presented peripheral constriction and relative central scotoma in the LE. Light and dark adaptation sensitivity curves showed abnormal thresholds for both cones and rods. No number at the Ishihara charts were recognized. Intraocular pressure was within normal limits. The slit lamp examination biomicroscopy of the anterior segment was normal for cornea, iris and lens appearance. Fundus examination revealed bilateral optic disc pallor, depigmented aspect of the choroidal and retinal structures, diffuse retinal dystrophy with absence of intraretinal pigment dispersion or vitreous abnormalities and arteriolar attenuation. Full-field scotopic and photopic electroretinograms showed reduced a-wave and b-wave amplitude responses and delayed implicit times. Multifocal ERG ring analysis documented reduced response amplitude densities in all examined areas from the foveal center up to 20° of foveal eccentricity in both eyes (LE &gt; RE). After reduced visual field in his LE, a large area of retinoschisis in the infero-temporal sector was observed by fundoscopy, which later progressed, resulting in full retinal detachment of the LE. The subject underwent to pars plana vitrectomy with silicon oil (30% polydimethylsiloxane, PDMS) tamponade. He underwent cataract surgery in his LE and to subsequent vitreo-retinal surgeries for relapsing retinal detachments in same eye (PDMS/perfluorocarbon liquid (PFCL)/PDMS tamponades exchange and intra-operatory laser treatment; PDMS/heavy silicon oil tamponades exchange and intra-operatory laser). One year later, he developed vitreo-retinal proliferation and retinal fibrosis in the LE, and visual acuity was hand motion; therefore, the subject underwent retinotomy and heavy silicon oil/PDMS tamponades exchange.
+At last evaluation (35 years), the subject presented with a good clinical condition. No cognitive deficit nor behavioral issues were observed, and no craniofacial dysmorphism and truncal obesity were noticed. An accurate endocrinological examination was uninformative. Anthropometric assessment displayed a height of 177.5 cm (+0.1 SD), weight of 95.70 kg (+1.6 SD), and OFC 60 cm (+0.2 SD) and BMI of 30.30 Kg/m2(+1.6 SD). Tanner stage was Ph5Pg5, with a testicular volume 20 mL bilaterally. The subject’s visual acuity was 0.8 Snellen in his RE and light perception in his LE. Fundus oculi showed the unmodified condition of RE and diffuse chorio-retinal atrophy in the LE, as for visible vitreo-retinal surgical outcomes. Ultrawide field fundus photography showed macular atrophy in absence of peripheral pigment and confirmed a “blonde” aspect of the retina (Figure 2A). Fundus autofluorescence (FAF) revealed an hypoautoflorescent area in the macula due to RPE atrophy and hyper/hypoautofluorescence mottling in the posterior pole and immediately outside the vascular arcades (Figure 2B). The SD-OCT showed a disruption of the outer retina, including ELM, ellipsoid zone and RPE with outer retinal debris at the level of the RPE in the parafoveal region (Figure 2C). Full-field flash scotopic (Figure 2D) and photopic ERG confirmed reduced a-wave and b-wave amplitude responses and delayed implicit times in the RE. Similarly, multifocal ERG ring analysis, recordable only in the RE, showed the worsening of the response amplitude densities in all examined areas (0–20°) (Figure 2E), as compared to the previous examinations. Similarly, Goldmann visual field in his RE showed progressive constriction of the peripheral isopters and a ring scotoma enclosed between 10–20° of the visual field (Figure 2F); it was not executable, however, in his LE. Color blindness was also confirmed. Neck and abdominal ultrasound assessment did not reveal any abnormality. Measurements of basal hormones by the anterior pituitary, glycaemia and insulin were within the normal range. Basal plasma leptin level was in the low normal range, showing no leptin resistance. During his follow-up, clinical and ophthalmological assessments of other family members (parents and younger brother) were unremarkable.
+Trio-based WES allowed to identify a homozygous splice siteTUBvariant (chr11:8122545G &gt; A, GRCh37.p13; c.1387 + 1G &gt; A,NM_177972.3) as the only clinically and functionally relevant event putatively linked to the disorder (Supplemental Table S1). The variant had previously been annotated in public databases (dbSNP, rs1040410003) with low frequency (gnomAD v3.1, MAF = 0.00001972) at the heterozygous state. It was classified as likely pathogenic (PVS1/PM2/PP5) according to the American College of Medical Genetics and Genomics-Association for Molecular Pathology (ACMG-AMP) criteria (ClinVar: VCV000865971.1) [14]. Sanger sequencing confirmed the homozygosity for the variant in the proband and the heterozygous status in the healthy parents and unaffected sib (Figure 1).
+Since the variant was predicted to affect the exon 11 donor splice site, the total RNA from patient-derived skin primary fibroblasts was used to characterize the impact of the nucleotide change on transcript processing. The cDNA fragment encompassing the relevant exons was amplified, confirming the presence of two aberrantly spliced products (Figure 3A). The two aberrant PCR amplicons were isolated from agarose gel, purified and sequenced via Sanger. The former (500 bp) was derived from skipping of the penultimate exon (exon 11, ENST00000299506.3), resulting in a premature termination codon (i.e., p.Glu406Argfs*4), while the latter (1172 bp) was the result of retention of intron 10, resulting in a TUB protein having a divergent 19-residue-long C-terminus and lacking the last 44 amino acids (p.Pro463Hisfs*19) (Figure 3B).
+In the patient’s skin fibroblasts, the predicted TUBGlu406Argfs*4protein was undetectable by Western blot [WB] analysis, while the TUBPro463Hisfs*19protein was poorly detectable likely due to accelerated degradation (Figure 3C, left panel). Consistently, the endogenous TUBPro463Hisfs*19level was partially rescued by blocking the proteasomal degradation pathway using MG132 (Figure 3C, right panel).
+To investigate the cellular localization of the mutated protein, cytoplasm and nuclear cell fractions were obtained and analyzed by WB. The results demonstrate that both the wild-type (wt) and mutant TUB proteins were almost exclusively localized in the nucleus (Figure 3D). This finding was also confirmed by confocal microscopy analysis that evidenced the nuclear localization of the TUB mutant (Figure 4A).
+Based on the documented role of TUB in early ciliogenesis [15], we assessed the localization of TUB at the cilium, but we failed to observe any consistent co-localization, possibly due to the low diffused levels of the protein in the cytoplasm To investigate the impact of defective TUB function on the morphogenesis of the primary cilium, a confocal analysis on primary fibroblasts was performed using antibodies against ARL13B, which localizes to primary cilia, and pericentrin, a component of the centrosome, which stains the basal body. As shown inFigure 4B, while almost all the control cells showed a primary cilium, 40% of the fibroblasts carrying the homozygous splice site variant inTUBdid not show a primary cilium. Moreover, while no significant difference was observed in ciliary axoneme length between the starved control and mutant cells, a large percentage of the latter showed an abnormal cilium morphology and a poorly defined and disorganized basal body (Figure 4C).
+The loss of TUB function was recently reported to underlie a novel IRD condition based on the identification of homozygosity for a 2 bp deletion (c.1194_1195delAG) causing the premature termination of the protein (p.Arg398Serfs*9) shared by three affected members of a single consanguineous family [10]. While the combination of retinal dystrophy and early onset obesity can be reminiscent of other disorders (e.g., Bardet–Biedl syndrome (MIM#PS209900) and Alstrom syndrome (MIM#203800)), the absence of other clinically relevant feature/sign was suggestive of a previously unreported ciliopathy [10]. In this paper, we report on a second disruptive variant (c.1387 + 1G &gt; A) affectingTUBin a subject with features that overlap with those previously described in the affected members of the original family.
+In the present and previously reported affected individuals, the ocular phenotype associated with defective TUB function is characterized by widespread retinal pigment epithelial (RPE) atrophy, deteriorating vision, the myopic and astigmatic refractive defect, the blonde fundus appearance, the ERG and OCT findings and progression of the disease (Figure 2). Notably, retinal detachment, without vitreous hemorrhage, was invariantly documented in the four individuals with biallelic inactivatingTUBvariants, suggesting that this feature likely represent a common finding in the disorder.
+Early onset obesity had previously been considered a major feature of the TUB-related condition [10], even though only two of three affected sibs were found obese (BMI &gt; 30), and the glycemic and lipid profiles in one of affected sibs were found within the normal range. The finding of obesity in the apparently healthy father (heterozygous carrier) suggests a possible co-occurring genetic event contributing to obesity in the family. In the present report, the clinical assessment of the affected individual documented increased weight (95.7 kg, +1.6 SD) and BMI (30.3, +1.6 SD), thus indicating overweight, in absence of other signs of obesity. Although evidence suggests that a defective TUB function may result in disturbances in insulin and leptin activity and obesity in mice [16,17,18,19], based on the collected findings, the relevance of TUB in human obesity requires further study. To assess whether TUB LoF could impact on hypothalamic pathways, food intake and adiposity, the metabolic profile of the affected individual was investigated. Accurate endocrinological examination did not reveal any abnormality, and the measurements of basal hormones by the anterior pituitary, glycaemia, insulin and leptin were within the normal range, thus ruling out insulin or leptin resistance. Consistently, instrumental investigations (X-ray and ultrasound analyses) documented no sign of glycogen accumulation in the internal organs. Consistently, the absence of significant changes in lipid storage was demonstrated by thin-layer chromatography (HPTLC) analysis in proband-derived fibroblast (Figure S1), allowing to confirm an apparently normal endocrine–metabolic profile in the affected individual. Of note, the Tubby protein has been involved in cochlear degeneration [20,21]. Based on this functional link, we evaluated the occurrence of hearing problems and cochlear degeneration, which were not observed.
+The homozygousTUBvariant was predicted to affect transcript processing, causing the skipping of exon 11 and intron retention, resulting in a frameshift with the premature termination of the TUB protein. mRNA analysis in proband-derived fibroblasts confirmed a disruptive impact of the splice site change documenting two aberrantly processed transcripts predicted to encode a 406-residue-long protein (p.Glu406Argfs*4) that probably is not able to proceed in protein synthesis, and a 481-residue-long protein (p.Pro463Hisfs*19) characterized by a divergent C-terminus characterized by accelerated degradation (Figure 3B). These findings confirm LoF as the pathomechanism underlying this disorder.
+Primary cilia are microtubule-based organelles that extend from the apical surface of the majority of mammalian cells. Cilia act as “cellular antennae”, receiving different inputs from the extracellular environment and transducing signals in response to stimuli [22]. A complex process required for proper cilia biogenesis function is the intraflagellar transport, which is required for assembling cilia and trafficking within primary cilia [23]. In this context, IFT-A has historically been believed to mediate retrograde intraflagellar transport inside the cilia and an IFT-A-binding domain at the TUB N-terminus has been demonstrated recently [24]. Moreover, co-localization between TUB and rootletin, the major structural component of the ciliary rootlet, has been observed in human retinal photoreceptors [10]. The use of a more informative in vitro model (e.g., induced pluripotent-stem-cell-derived retinal-pigment epithelium cells) and experimental strategies (e.g., siRNA-mediated TUB silencing) is required to appreciate more accurately the functional relevance of TUB in an appropriate cellular context.
+In summary, we confirm the link between TUB LoF and a new condition of human retinal ciliopathy and provide evidence of an altered cilium morphology/biogenesis in patient-derived fibroblasts. In fact, these cells displayed a reduced number of cilia when compared to the control cells, with a poorly defined and disorganized basal body structure, which are expected to prevent normal protein trafficking along the cilium. While these findings could explain the degeneration of photoreceptors characterizing this disorder, a relatively overall mild presentation has been associated with mutations in this gene. Multiple factors might contribute to this picture. First, the functional relevance of TUB in the context of ciliogenesis and cilium function might vary in different cell lineages. Second, functional compensation exerted by other related proteins might contribute to buffer the severity of the endophenotype. Third, specific cell lineages (e.g., rod and cone cells) might be particularly sensitive to TUB LoF. The collection of additional patients with biallelic variants in the gene will allow a more accurate characterization of the clinical spectrum associated with TUB LoF. Based on these considerations, TUB loss of function could be considered as responsible for a novel form of isolated retinal ciliopathy.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -918,77 +829,77 @@
     HGNC record ID: HGNC:12406
     Primary gene symbol: TUB
     Official HGNC gene name: TUB bipartite transcription factor
-    Biomedical text context (may include PMID)
+    Biomedical text context
     Task:
-    Determine whether the alias symbol in the given text refers to the gene represented by the provided HGNC record ID.
+    Determine whether the alias symbol in the given text represents the gene associated with the provided HGNC record ID
+    as an alternate abbreviation of the official HGNC gene symbol.
+    Classify the alias symbol as an Alternate Abbreviation only if it is explicitly expanded in the text to the official
+    HGNC gene name, or to a phrase that is nearly identical in wording and meaning.
+    The mere presence of both the alias symbol and the official HGNC gene name in the text is not sufficient. 
+    The text must explicitly link the alias symbol to the official gene name through an expansion 
+    (e.g., “ALIAS (Official Gene Name)” or equivalent phrasing).
+    Examples:
+    1-
+    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step 
+    procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration 
+    chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
+    Alias gene symbol: A1B
+    Official HGNC gene name: alpha-1-B glycoprotein
+    Primary gene symbol: A1BG
+    2-
+    Text: “Editing of apolipoprotein (apo) B mRNA is mediated by an enzyme-complex that consists of the catalytic 
+    cytidine deaminase APOBEC-1 and the mRNA binding protein APOBEC-1 complementation factor or APOBEC-1 stimulating protein (ACF/ASP).”
+    Alias gene symbol: ASP
+    Official HGNC gene name: APOBEC1 complementation factor
+    Primary gene symbol: A1CF
     Rules:
-    If the text does not support that the alias refers to the provided gene, return:
-    "alias_symbol_represents_primary_gene": "NO"
-    "alternate_abbreviation": ""
-    "evidence": ""
-    If the text does support the gene identity, set "alias_symbol_represents_primary_gene": "YES" and 
-    determine whether the alias symbol in the given text is an alternate abbreviation for the primary gene symbol.
     If the text does not support that the alias is an alternate abbreviation, return:
     "alternate_abbreviation": "NO"
     "evidence": ""
     If the text does support that the alias is an alternate abbreviation, set "alternate_abbreviation": "YES"
-    ALTERNATE ABBREVIATION → alias is expanded to a phrase identically matching the official HGNC gene name
-    ALTERNATE ABBREVIATION — POSITIVE EXAMPLE
-    Text: “Alpha 1-beta glycoprotein (A1B) was purified to homogeneity from human plasma using a three-step procedure involving pseudo-ligand affinity chromatography on immobilized Cibacron Blue 3-GA, gel filtration chromatography on Sephadex G-200 and ion-exchange chromatography on DEAE Affigel Blue.”
-    Alias gene symbol: A1B
-    Primary gene symbol: A1BG
     Evidence must be one exact sentence copied verbatim from the text.
     Do not infer relationships or paraphrase evidence.
     Output (Strict):
-    Output only one JSON object. No explanations. No markdown.
+    Output only one JSON object. No markdown.
     {
     "pmid": "",
     "alias_symbol": "",
     "primary_gene_symbol": "",
     "name": "",
-    "alias_symbol_represents_primary_gene": "YES or NO",
     "alternate_abbreviation": "YES or NO",
     "evidence": ""
     }
-PMID: 36650547
-Full Text: Retinitis pigmentosa (RP) is the most common type of inherited retinopathy. At least 69 genes for RP have been identified. A significant proportion of RP, however, remains genetically unsolved. In this study, the genetic basis of a Chinese consanguineous family with presumed autosomal recessive retinitis pigmentosa (arRP) was investigated.
-Overall ophthalmic examinations, including funduscopy, decimal best-corrected visual acuity, axial length and electroretinography (ERG) were performed for the family. Genomic DNA from peripheral blood of the proband was subjected to whole exome sequencing. In silico predictions, structural modelling, and minigene assays were conducted to evaluate the pathogenicity of the variant.
-A novel homozygous variant (NM_003320.4: c.1379A &gt; G) in theTUBgene was identified as a candidate pathogenic variant in this parental consanguineous pedigree. This variant co-segregated with the disease in this pedigree and was absent in 118 ethnically matched healthy controls. It’s an extremely rare variant that is neither deposited in population databases (1000 Genomes, ExAC, GnomAD, or Exome Variant Server) nor reported in the literature. Phylogenetic analysis indicated that the Asn residue at codon 460 of TUB is highly conserved across diverse species from tropicalis to humans. It was also completely conserved among the TUB, TULP1, TULP2, and TULP3 family proteins. Multiple bioinformatic algorithms predicted that this variant was deleterious.
-A novel missense variant inTUBwas identified, which was probably the pathogenic basis for arRP in this consanguineous family. This is the first report of a homozygous missense variant inTUBfor RP.
-The online version contains supplementary material available at 10.1186/s12920-023-01430-0.
-Retinitis pigmentosa (RP), a highly heterogenous genetic disorder, is the most common inherited retinopathy induced by progressive loss of photoreceptor cells and subsequent degeneration of the retina. Typical clinical manifestations of RP include night blindness, bone-spicule deposits, gradual loss of central vision, waxy optic disc, and attenuated retinal arteries. The prevalence of RP varied significantly among ethnic groups ranging from 1/1000 to 1/ 5000 worldwide [1–3]. RP can be inherited in classic Mendelian inheritance (including 20–25% autosomal recessive, 15–20% autosomal dominant, and 10–15% X-linked) [2] as well as rarely mitochondrial [4] and digenic [5] inheritance. Although most cases of RP are monogenic, the disease is highly genetically heterogeneous. To date, at least 69 genes have been identified for nonsyndromic RP (including 23 genes for adRP, 44 genes for arRP, and 2 for xlRP) (RetNet,https://sph.uth.edu/retnet, updated October 7, 2022). Generally, broad functions of the identified genes can be classified into five groups: RNA splicing, cellular structure, retinal metabolism, photo-transduction, and tissue development and maintenance [6]. These genes, however, account for no more than 60% of all patients [7,8], and the rest remain genetically unsolved. In China, mutations in about 34 genes have been detected, among which the top seven genes areCYP4V2,RHO,USH2A,RPGR,CRB1,RP2, andCHM, accounting for about two thirds of the RP-related mutations in our Chinese population [9]. Identification of additional genes or novel variants is a prerequisite for genetic counseling, and it’s key to better define the genetic etiology of RP. The remarkable genetic and phenotypic heterogeneity of arRP, however, remains a major obstacle in the identification of pathogenic variants. In addition, some homozygous variants are too rare to be screened in general case–control studies. Whereas pedigrees with hereditary diseases, especially consanguineous pedigrees, are extremely valuable resources for genetic studies of inherited diseases such as arRP.
-TUB(MIM #601197), also known asrd5orRDOB, maps to 11p15.4 and encodes the tubby-bipartite transcription regulator [10,11]. Abundantly expressed in the retina, brain, and cochlea [12–14] with dual localization to the plasma membrane and nucleus [10],TUBhas been implicated in energy balance [15,16], retinal degeneration [12], and neuronal regulation in mice [17]. However, the underlying molecular mechanism remains to be fully elucidated. Previous studies have demonstrated that loss-of-function mutations inTubor Drosophila king tubby(ktub)cause retinal degeneration in both mice and Drosophila [18–21].Mutations inTUBfor retinal-associated diseases in humans, however, are extremely rare. Thus far, only one mutation inTUBfor arRP have been reported in the literature, in which a homozygous frameshift variant resulted in retinal dystrophy, hearing loss, and obesity in a consanguineous UK Caucasian family [12]. Here, we describe a novel rare homozygousTUBvariant (NM_003320.4, c.1379A &gt; G, p.Asn460Ser) in a Chinese consanguineous family with typical arRP. In silico predictions, structural modelling, and experimental studies were conducted to evaluate the pathogenicity of this variant.
-A Chinese parental consanguineous family (living in the remote countryside of Hunan Province) with arRP (Fig.1) and 118 ethnicity and region-matched healthy adults were enrolled by the Department of Ophthalmology of Hunan Provincial People’s Hospital. Overall ophthalmic examinations including funduscopy, decimal best-corrected visual acuity (BCVA), axial length and electroretinography (ERG), were performed by senior ophthalmologists. This study was approved by the Ethics Committee of Hunan Normal University.Fig. 1Pedigree of the arRP family, Fundus and OCT images of the proband.APedigree of the parental consanguineous Chinese family with RP (red arrow indicates the proband of this pedigree, slashed symbols represent deceased members).BFundus images of the proband’s two eyes (R: right, L: left).COptical coherence tomography (OCT) images of the proband (R: right, L: left)
-Pedigree of the arRP family, Fundus and OCT images of the proband.APedigree of the parental consanguineous Chinese family with RP (red arrow indicates the proband of this pedigree, slashed symbols represent deceased members).BFundus images of the proband’s two eyes (R: right, L: left).COptical coherence tomography (OCT) images of the proband (R: right, L: left)
-Genomic DNA from peripheral blood leukocytes of the proband was subjected to WES analysis on Illumina NovaSeq 6000 at the Berry Genomics as described previously [22]. Briefly, data were aligned to hg38/GRCh38 with BWA and the average coverage depth was about 100×. The VeritaTrekker® Variant Detection System, Enliven® Data Annotation, and Interpretation System were used to perform SNP, CNV, indel discovery, and genotyping. All nonsynonymous variants (NSVs) including single nucleotide variants (SNVs), splicing sites, and indels were selected and filtered against the dbSNP137 database, the ExAC, gnomAD, 1000 Genomes phase3, and the MyGenostics local database. The variants with a minor allele frequency (MAF) less than 1% were kept as candidates. Pathogenicity of the mutants were assessed following the guidelines of the American College of Medical Genetics and Genomics (ACMG) [23,24]. Benign or Likely-benign mutations were filtered out.
-Primers (Additional file1: Table S1) used to amplify the fragments harboring candidate variants were designed using Primer3 (https://bioinfo.ut.ee/primer3-0.4.0). Samples of 118 ethnicity and region matched healthy controls were also sequenced to screen variants inTUB.SIFT (Sorting Intolerant from Tolerant,http://sift.jcvi.org), Mutation Taster (http://www.mutationtaster.org), PROVEAN (Protein Variation Effect Analyzer,http://provean.jcvi.org), and CADD_Phre (Combined Annotation Dependent Depletion,http://cadd.gs.washington.edu) were used to evaluate the potential pathogenicity of the variant with default parameters. Novopro (https://www.novopro.cn/tools/protein-hydrophilicity-plot.html) was used to evaluate the hydrophobicity of the mutant TUB protein. The sequence alignment of different species were performed using ClustalW (https://www.ebi.ac.uk/Tools/msa/clustalo). The three dimensional protein model was generated with PyMOL (http://www.schrodinger.com/pymol/) [25].
-The 2240-bp DNA fragments ofTUB(including exons 10–12 and introns 10–11) were amplified from the genomic DNA of the proband or a healthy control with primers as the following:TUB-BamHI-F: 5′- aagcttggtaccgagctcggatccGTCCAACTTGATGGGCACCAAGTTCACT-3′;TUB-XhoI-R: 5′- ttaaacgggccctctagactcgagGGTCATTGCCATGGATGATCTGGAAGTT-3′. After treatment with restriction endonucleases BamHI and XhoI, the amplified fragments were cloned into pMini-CopGFP using the KOD-Plus Neo Kit (TOYOBO CO., OSAKA, JAPAN). The recombinant constructs were confirmed by Sanger sequencing. The wild type (pMini-CopGFP-TUB-WT) and mutant type (pMini-CopGFP-TUB-MT) recombinant constructs were then transiently transfected into two commonly used mammalian cell lines (APRE-19 and 293 T cells) following the protocol provided by the TurboFect kit (Thermo, USA). RT-PCR was performed to obtain the target fragments of humanTUBgene with primers as the following: MiniRT-F: 5’-GGCTAACTAGAGAACCCACTGCTTA-3’;TUB-RT-R: 5’-GGTCATTGCCATGGATGATCTG-3’. The amplified fragments were detected on 1.5% agarose gel and further verified by Sanger sequencing.
-In this five-generation parental consanguineous Chinese pedigree (Fig.1A), the proband (IV:4) and three healthy individuals (IV:5, V: 1, and V: 2) were enrolled in this study. Comprehensive ophthalmic examinations were performed for them. The proband exhibited night blindness and decreased visual acuity since the age of 16, and received a well-defined clinical diagnosis of RP at age 35. The last examination was carried out at age 59 with a BCVA of index/20 cm and 0.25 in the right and left eyes. The axial length was 22.40 mm in the right eye and 23.60 mm in the left eye. Funduscopy displayed spread attenuated arterioles, waxy optic disc, tunnel field, diffused bone-spicule deposition, and atrophy of the choroid in both eyes (Fig.1B). OCT images showed perifoveal retinal thinning in both fundi (Fig.1C). At ages 53 and 59, the proband underwent cataract surgery in the right eye and left eye, respectively. In addition, the proband exhibited no other related disorders nor additional phenotypes such as obesity or hearing deficits as described in other report [12]. The husband and two daughters of the proband were asymptomatic with normal funduscopic observations.
-WES was performed for the proband. After mapping to the human reference genome (hg38), we achieved 3.2G bases with a mean sequencing depth of 100×, among which ≥ 20 × read depth were approximately 98.92%. A total of 53,556 genetic variants including indels and SNPs were detected in the initial WES data of the proband. After exclusion of high-frequency variants in thegnomAD, 1000G phase III, ExAC, and MyGenostics local database, four candidate variants including three heterozygous variants inRAX2, RP1,andPITPNM3,and a homozygous variant inTUB, were remained as suspected pathogenic variants (Additional file1: Table S2). Further co-segregation investigation and genotype–phenotype correlation analysis excluded the pathogenicity of the three heterozygous variants inRAX2, RP1andPITPNM3.A novel homozygous mutation inTUB(c.1379A &gt; G. p.Asn460Ser) remained as the only candidate variant, and no additional causative mutations in all other known RP genes were detected.
-Further Sanger sequencing validated the proband (IV: 4) harbored theTUBvariant in a homozygous state, whereas his husband (IV: 5) was homozygous for the wild type alleles and two unaffected daughters (V: 1, V:2) were heterozygous carriers for the variant (Fig.2). The homozygous variant, based on Sanger sequencing, was verified to co-segregate with the RP phenotype in an autosomal recessive inheritance manner and was excluded from 118 ethnically and regionally matched normal controls. Although the same variant deposited in ClinVar (variation ID: 1,091,773) was interpreted as “likely benign”, we propose that such “likely benign” interpretation is invalid since detailed information about the variant including the variant type, the inheritance pattern, the ethnic group, affected status, or allele origin were not provided. Furthermore, the same variant was also deposited in dbSNP as a SNP (rs189328202) with a frequency of 0.00080, 0.000159 and 0.00005 in 1000G, ExAC, and GnomAD, respectively (Table1). Importantly, the variant was not reported in a homozygous state in all public database (Table1). This novel homozygous variant (c.1379A &gt; G. p.Asn460Ser) inTUBappeared to be extremely rare as it was not reported in the literature either.Fig. 2Co-segragation analysis of the c.1379A &gt; G (p.Asn460SerSer) variant inTUB.ASequences of the homozygous c.1379A &gt; G variant in the proband (IV:4);B,CSequences of the heterozygous carries (V:1, V:2) of the family;DSequences of healthy member (IV:5) of the familyTable 1Allele frequency (G) of c.1379A &gt; G in exon 11 ofTUB(rs189328202) among different population (Released April 9, 2022)Number of Homozygotes (G/G)Number of Heterozygotes (A/G)Ref Allele/Alt AlleleGlobalEast AsianSouth AsianEuropeAmericanAfrican1000G0/50084/5008A = 0.99920A = 0.9960A = 1.000A = 1.000A = 1.000A = 1.000G = 0.00080G = 0.0040G = 0.000G = 0.000G = 0.000G = 0.000GnomAD-Genomes0/1401707/140170A = 0.99995A = 0.9981A = 1.000A = 1.000A = 1.000A = 1.000G = 0.00005G = 0.0019G = 0.000G = 0.000G = 0.000G = 0.000GnomAD-Exomes0/25119449/251194A = 0.999805A = 0.99904A = 0.999993A = 1.000A = 1.000G = 0.000195G = 0.00096G = 0.000007G = 0.000G = 0.000ExAC0/11928819/119288A = 0.999841A = 0.99923A = 1.000A = 1.000A = 1.000G = 0.000159G = 0.00077G = 0.000G = 0.000G = 0.000
-Co-segragation analysis of the c.1379A &gt; G (p.Asn460SerSer) variant inTUB.ASequences of the homozygous c.1379A &gt; G variant in the proband (IV:4);B,CSequences of the heterozygous carries (V:1, V:2) of the family;DSequences of healthy member (IV:5) of the family
-Allele frequency (G) of c.1379A &gt; G in exon 11 ofTUB(rs189328202) among different population (Released April 9, 2022)
-The effect of the non-synonymous variant inTUB(c.1379A &gt; G, p.Asn460Ser) was predicted to be deleterious by PROVEAN with a score of -4.193 (a score ≤ -2.5 is considered deleterious) and damaging by SIFT with a score of 0.035 (a score of 0–0.05 is considered damaging). It was also predicted to be disease-causing by MutationTaster with a score of ~ 1 and damaging by CADD_Phred with a score of 24 (Table2). The hydrophobicity analysis with regard to the changed residue at codon 460 in TUB indicated a lower hydrophilicity than that of the wild type (Fig.3A). Phylogenetic analysis indicated that the Asn residue at codon 460 of TUB is highly conserved across diverse species fromtropicalisto humans (Fig.3B). Further structural modeling (Fig.3C) demonstrated that the changed residue at codon 460 of TUB may contribute to an abnormal TUB conformation. According to the ACMG guidelines [23,24], the c.1379A &gt; G variant inTUBcould be considered as “likely pathogenic”.Table 2Functional predictions of the homozygous mutation of TUB in this studyGeneAccession numberChromosome positionExonVariant TypeVariantMutation TasteraPROVEANb(cutoff = − 2.5)SIFTb(cutoff = 0.05)CADD_Phrec(cutoff = 20)TUBNM_003320.511p15.411Missense Variantc.1379A &gt; G p.Asn460Ser~ 1− 4.190.03524Disease-causingDeleteriousDamagingDamagingahttps://www.mutationtaster.org/bhttp://provean.jcvi.orgchttp://cadd.gs.washington.eduFig. 3Hydrophobicity analysis of the wild and mutant proteins, multiple alignment of the amino acid sequences around Asn460 in different species, and predicted model structures of the human TUB protein.AHydrophobicity analysis performed by Novopro, indicating a slight decrease in hydrophilicity caused by the variant.BMultiple-sequence alignments of TUB around Asn460 among different species, indicating that this variant was highly conserved among species.CPredicted structures of the human TUB protein (residues 289 through 561) using PyMOL. The p.Asn460Ser variant inTUBis indicated with ball-and-stick models. N, asparagine; S, serine
-Functional predictions of the homozygous mutation of TUB in this study
-ahttps://www.mutationtaster.org/
-bhttp://provean.jcvi.org
-chttp://cadd.gs.washington.edu
-Hydrophobicity analysis of the wild and mutant proteins, multiple alignment of the amino acid sequences around Asn460 in different species, and predicted model structures of the human TUB protein.AHydrophobicity analysis performed by Novopro, indicating a slight decrease in hydrophilicity caused by the variant.BMultiple-sequence alignments of TUB around Asn460 among different species, indicating that this variant was highly conserved among species.CPredicted structures of the human TUB protein (residues 289 through 561) using PyMOL. The p.Asn460Ser variant inTUBis indicated with ball-and-stick models. N, asparagine; S, serine
-The minigenes pMini-CopGFP-TUB-WT/MT (Fig.4A) were constructed to explore the splicing effect of this variant. The genomic region spanning from Exon10 to Exon12 ofTUB-WT/TUB-MT were cloned into pMini-CopGFP respectively. RT-PCR analysis showed a single band with the expected size of 460 bp for both WT and MT minigenes in two different cell lines (Fig.4B). And Sanger sequencing confirmed the normal splicing of the minigenes (Exon 10- Exon11- Exon12) (Fig.4C, D), indicating impact of the variant on splicing could be basically ruled out.Fig. 4Minigene assay for the c.1379 A &gt; G variant inTUB.ASchematic illustration of cloned vectors (pMini-CopGFP-TUB minigene), red * indicates the variant site.BElectrophoresis of RT-PCR fragments from APRE-19 cells and 293 T cells (original gel is presented in Additional file1: Fig. S2).CSplicing sequences confirmed by Sanger sequencing.DSchematic diagram shows no effect of theTubvariant (c.1379A &gt; G) on splicing. WT, wild-type; MT, mutant-type
-Minigene assay for the c.1379 A &gt; G variant inTUB.ASchematic illustration of cloned vectors (pMini-CopGFP-TUB minigene), red * indicates the variant site.BElectrophoresis of RT-PCR fragments from APRE-19 cells and 293 T cells (original gel is presented in Additional file1: Fig. S2).CSplicing sequences confirmed by Sanger sequencing.DSchematic diagram shows no effect of theTubvariant (c.1379A &gt; G) on splicing. WT, wild-type; MT, mutant-type
-In the current study, we examined a consanguineous family with arRP from central south China and detected a novel homozygous variant (c.1379 G &gt; A: p.Asn460Ser) inTUB. This variant co-segregated with the disease in an autosomal recessive manner and was absent in 118 ethnically matched healthy controls. This homozygous variant has not been reported in the literature or deposited in existing databases including gnomAD, 1000G phase3, ExAC, or dbSNP, indicating that this variant is rare. Multiple bioinformatic algorithms predicted that this variant was deleterious or damaging. Conservative analysis showed the codon Asn460 fallen within a highly conserved region across diverse species (Fig.3B). Further structural modeling showed that amino acid substitution (Ser) of the variant at residue Asn460 could affect the protein conformation, the binding ability of the tubby domain [26], as well as the solubility and stabilization of the mutant protein [27]. Taken together, these data strongly supported the hypothesis that this novelTUBvariant (c.1379 A &gt; G: p. Asn460Ser) might be the genetic basis of arRP in this Chinese consanguineous family.</t>
+PMID: 9390831
+Full Text: These authors contributed equally to this work.
+These authors jointly coordinated this work.
+Inherited retinal degeneration (IRD) represents a clinically variable and genetically heterogeneous group of disorders characterized by photoreceptor dysfunction. These diseases typically present with progressive severe vision loss and variable onset, ranging from birth to adulthood. Genomic sequencing has allowed to identify novel IRD-related genes, most of which encode proteins contributing to photoreceptor-cilia biogenesis and/or function. Despite these insights, knowledge gaps hamper a molecular diagnosis in one-third of IRD cases. By exome sequencing in a cohort of molecularly unsolved individuals with IRD, we identified a homozygous splice site variant affecting the transcript processing of TUB, encoding the first member of the Tubby family of bipartite transcription factors, in a sporadic case with retinal dystrophy. A truncating homozygous variant in this gene had previously been reported in a single family with three subjects sharing retinal dystrophy and obesity. The clinical assessment of the present patient documented a slightly increased body mass index and no changes in metabolic markers of obesity, but confirmed the occurrence of retinal detachment. In vitro studies using patient-derived fibroblasts showed the accelerated degradation of the encoded protein and aberrant cilium morphology and biogenesis. These findings definitely link impaired TUB function to retinal dystrophy and provide new data on the clinical characterization of this ultra-rare retinal ciliopathy.
+Inherited retinal degeneration (IRD) occurs in a clinically variable and genetically heterogeneous group of conditions characterized by photoreceptor degeneration and/or dysfunction [1]. The prevalence of monogenic IRD is estimated as 1 in 2000 individuals, affecting more than 2 million people worldwide [2]. This group of disorders typically present with severe vision loss that can be progressive, having an onset ranging from birth to late adulthood. Severe visual impairment affects mobility and independence, posing relevant psychological and economic burdens [3]. In the last ten years, genomic sequencing has allowed the identification of several genes implicated in IRD (for an updated list see the RetNet database,https://sph.uth.edu/retnet/). These genes encode proteins that have different roles in visual function, contributing to key processes in the cells of the pigmented cell layer and neurosensory retina [4,5]. Notably, retinal degeneration is frequently observed in ciliopathies, and a portion of IRD-related genes codifies for proteins involved in biogenesis and the maintenance of photoreceptor primary cilium [6,7,8,9]. Among these genes,TUB[MIM #601197], which encodes the first member of the Tubby family of bipartite transcription factors, has recently reported to be associated with a novel condition characterized by retinal dystrophy and obesity [MIM #616188] [10]. A truncating homozygousTUBvariant [c.1194_1195delAG, p.Arg398Serfs*9] was identified in a single family with three affected members, suggesting loss of function (LoF) as the pathomechanism underlying the disorder. The TUB family of transcription factors counts four members in vertebrates (TUB, TULP1, TULP2 and TULP3), sharing a similar domain organization including a highly conserved C-terminal domain mediating DNA binding and a divergent N-terminal region encompassing the nuclear localization signal and the transcriptional activation domain implicated in protein–protein binding [11]. A conserved region at the N-terminus enables some members of the Tubby family, including TUB, to bind to the ciliary intraflagellar transport A protein (IFTAP) [12]. Similar to the other members of the TULP family, TUB is also implicated in the control of the initiation of phagocytosis, facilitating the removal of apoptotic cells or cellular debris by retinal pigmented epithelium (RPE) cells and macrophages [13]. Since the original report, no other subject carrying biallelicTUBvariants has been described.
+In this study, we report on an additional subject with retinal dystrophy carrying a homozygous LoF variant inTUB. In vitro analyses provide evidence of the disruptive functional impact of the variant onTUBtranscript processing. We also show that the loss of TUB is associated with a defective cilium morphology and biogenesis in the primary patient’s fibroblasts. Our findings confirm the involvement of defective TUB function in retinal dystrophy and define this disorder as a novel ciliopathy.
+The proband is a 35-year-old male, the first child of healthy non-consanguineous parents of European descent (Figure 1). Family history was negative for retinal diseases or other congenital defects. The proband was born at term after an uneventful pregnancy. Length and weight at birth were reported as within the normal range. Apgar score was 8–10. No hearing impairment and/or learning difficulties were documented during the first year of age.
+At 5 years, the subject required consulting ophthalmologists for referring color blindness. A “blonde” aspect of the fundus oculi was observed and reduced full-field flash photopic and scotopic electroretinogram (ERG) responses were recorded. Visual acuity was not investigated at that time. Ophthalmological assessment at 26 years was suggestive of cone-rod dystrophy. Visual acuity was 0.8 Snellen in his right eye (RE) with myopic and astigmatic refractive error (RE: -4.50 dioptre sphere and -1 dioptre cylinder at 20°), and 0.2 Snellen in his left eye (LE) with myopic refractive error (LE: -2.00 dioptre sphere). Goldmann visual field was generally constricted, with reduced sensitivity in the superior central field in the RE and presented peripheral constriction and relative central scotoma in the LE. Light and dark adaptation sensitivity curves showed abnormal thresholds for both cones and rods. No number at the Ishihara charts were recognized. Intraocular pressure was within normal limits. The slit lamp examination biomicroscopy of the anterior segment was normal for cornea, iris and lens appearance. Fundus examination revealed bilateral optic disc pallor, depigmented aspect of the choroidal and retinal structures, diffuse retinal dystrophy with absence of intraretinal pigment dispersion or vitreous abnormalities and arteriolar attenuation. Full-field scotopic and photopic electroretinograms showed reduced a-wave and b-wave amplitude responses and delayed implicit times. Multifocal ERG ring analysis documented reduced response amplitude densities in all examined areas from the foveal center up to 20° of foveal eccentricity in both eyes (LE &gt; RE). After reduced visual field in his LE, a large area of retinoschisis in the infero-temporal sector was observed by fundoscopy, which later progressed, resulting in full retinal detachment of the LE. The subject underwent to pars plana vitrectomy with silicon oil (30% polydimethylsiloxane, PDMS) tamponade. He underwent cataract surgery in his LE and to subsequent vitreo-retinal surgeries for relapsing retinal detachments in same eye (PDMS/perfluorocarbon liquid (PFCL)/PDMS tamponades exchange and intra-operatory laser treatment; PDMS/heavy silicon oil tamponades exchange and intra-operatory laser). One year later, he developed vitreo-retinal proliferation and retinal fibrosis in the LE, and visual acuity was hand motion; therefore, the subject underwent retinotomy and heavy silicon oil/PDMS tamponades exchange.
+At last evaluation (35 years), the subject presented with a good clinical condition. No cognitive deficit nor behavioral issues were observed, and no craniofacial dysmorphism and truncal obesity were noticed. An accurate endocrinological examination was uninformative. Anthropometric assessment displayed a height of 177.5 cm (+0.1 SD), weight of 95.70 kg (+1.6 SD), and OFC 60 cm (+0.2 SD) and BMI of 30.30 Kg/m2(+1.6 SD). Tanner stage was Ph5Pg5, with a testicular volume 20 mL bilaterally. The subject’s visual acuity was 0.8 Snellen in his RE and light perception in his LE. Fundus oculi showed the unmodified condition of RE and diffuse chorio-retinal atrophy in the LE, as for visible vitreo-retinal surgical outcomes. Ultrawide field fundus photography showed macular atrophy in absence of peripheral pigment and confirmed a “blonde” aspect of the retina (Figure 2A). Fundus autofluorescence (FAF) revealed an hypoautoflorescent area in the macula due to RPE atrophy and hyper/hypoautofluorescence mottling in the posterior pole and immediately outside the vascular arcades (Figure 2B). The SD-OCT showed a disruption of the outer retina, including ELM, ellipsoid zone and RPE with outer retinal debris at the level of the RPE in the parafoveal region (Figure 2C). Full-field flash scotopic (Figure 2D) and photopic ERG confirmed reduced a-wave and b-wave amplitude responses and delayed implicit times in the RE. Similarly, multifocal ERG ring analysis, recordable only in the RE, showed the worsening of the response amplitude densities in all examined areas (0–20°) (Figure 2E), as compared to the previous examinations. Similarly, Goldmann visual field in his RE showed progressive constriction of the peripheral isopters and a ring scotoma enclosed between 10–20° of the visual field (Figure 2F); it was not executable, however, in his LE. Color blindness was also confirmed. Neck and abdominal ultrasound assessment did not reveal any abnormality. Measurements of basal hormones by the anterior pituitary, glycaemia and insulin were within the normal range. Basal plasma leptin level was in the low normal range, showing no leptin resistance. During his follow-up, clinical and ophthalmological assessments of other family members (parents and younger brother) were unremarkable.
+Trio-based WES allowed to identify a homozygous splice siteTUBvariant (chr11:8122545G &gt; A, GRCh37.p13; c.1387 + 1G &gt; A,NM_177972.3) as the only clinically and functionally relevant event putatively linked to the disorder (Supplemental Table S1). The variant had previously been annotated in public databases (dbSNP, rs1040410003) with low frequency (gnomAD v3.1, MAF = 0.00001972) at the heterozygous state. It was classified as likely pathogenic (PVS1/PM2/PP5) according to the American College of Medical Genetics and Genomics-Association for Molecular Pathology (ACMG-AMP) criteria (ClinVar: VCV000865971.1) [14]. Sanger sequencing confirmed the homozygosity for the variant in the proband and the heterozygous status in the healthy parents and unaffected sib (Figure 1).
+Since the variant was predicted to affect the exon 11 donor splice site, the total RNA from patient-derived skin primary fibroblasts was used to characterize the impact of the nucleotide change on transcript processing. The cDNA fragment encompassing the relevant exons was amplified, confirming the presence of two aberrantly spliced products (Figure 3A). The two aberrant PCR amplicons were isolated from agarose gel, purified and sequenced via Sanger. The former (500 bp) was derived from skipping of the penultimate exon (exon 11, ENST00000299506.3), resulting in a premature termination codon (i.e., p.Glu406Argfs*4), while the latter (1172 bp) was the result of retention of intron 10, resulting in a TUB protein having a divergent 19-residue-long C-terminus and lacking the last 44 amino acids (p.Pro463Hisfs*19) (Figure 3B).
+In the patient’s skin fibroblasts, the predicted TUBGlu406Argfs*4protein was undetectable by Western blot [WB] analysis, while the TUBPro463Hisfs*19protein was poorly detectable likely due to accelerated degradation (Figure 3C, left panel). Consistently, the endogenous TUBPro463Hisfs*19level was partially rescued by blocking the proteasomal degradation pathway using MG132 (Figure 3C, right panel).
+To investigate the cellular localization of the mutated protein, cytoplasm and nuclear cell fractions were obtained and analyzed by WB. The results demonstrate that both the wild-type (wt) and mutant TUB proteins were almost exclusively localized in the nucleus (Figure 3D). This finding was also confirmed by confocal microscopy analysis that evidenced the nuclear localization of the TUB mutant (Figure 4A).
+Based on the documented role of TUB in early ciliogenesis [15], we assessed the localization of TUB at the cilium, but we failed to observe any consistent co-localization, possibly due to the low diffused levels of the protein in the cytoplasm To investigate the impact of defective TUB function on the morphogenesis of the primary cilium, a confocal analysis on primary fibroblasts was performed using antibodies against ARL13B, which localizes to primary cilia, and pericentrin, a component of the centrosome, which stains the basal body. As shown inFigure 4B, while almost all the control cells showed a primary cilium, 40% of the fibroblasts carrying the homozygous splice site variant inTUBdid not show a primary cilium. Moreover, while no significant difference was observed in ciliary axoneme length between the starved control and mutant cells, a large percentage of the latter showed an abnormal cilium morphology and a poorly defined and disorganized basal body (Figure 4C).
+The loss of TUB function was recently reported to underlie a novel IRD condition based on the identification of homozygosity for a 2 bp deletion (c.1194_1195delAG) causing the premature termination of the protein (p.Arg398Serfs*9) shared by three affected members of a single consanguineous family [10]. While the combination of retinal dystrophy and early onset obesity can be reminiscent of other disorders (e.g., Bardet–Biedl syndrome (MIM#PS209900) and Alstrom syndrome (MIM#203800)), the absence of other clinically relevant feature/sign was suggestive of a previously unreported ciliopathy [10]. In this paper, we report on a second disruptive variant (c.1387 + 1G &gt; A) affectingTUBin a subject with features that overlap with those previously described in the affected members of the original family.
+In the present and previously reported affected individuals, the ocular phenotype associated with defective TUB function is characterized by widespread retinal pigment epithelial (RPE) atrophy, deteriorating vision, the myopic and astigmatic refractive defect, the blonde fundus appearance, the ERG and OCT findings and progression of the disease (Figure 2). Notably, retinal detachment, without vitreous hemorrhage, was invariantly documented in the four individuals with biallelic inactivatingTUBvariants, suggesting that this feature likely represent a common finding in the disorder.
+Early onset obesity had previously been considered a major feature of the TUB-related condition [10], even though only two of three affected sibs were found obese (BMI &gt; 30), and the glycemic and lipid profiles in one of affected sibs were found within the normal range. The finding of obesity in the apparently healthy father (heterozygous carrier) suggests a possible co-occurring genetic event contributing to obesity in the family. In the present report, the clinical assessment of the affected individual documented increased weight (95.7 kg, +1.6 SD) and BMI (30.3, +1.6 SD), thus indicating overweight, in absence of other signs of obesity. Although evidence suggests that a defective TUB function may result in disturbances in insulin and leptin activity and obesity in mice [16,17,18,19], based on the collected findings, the relevance of TUB in human obesity requires further study. To assess whether TUB LoF could impact on hypothalamic pathways, food intake and adiposity, the metabolic profile of the affected individual was investigated. Accurate endocrinological examination did not reveal any abnormality, and the measurements of basal hormones by the anterior pituitary, glycaemia, insulin and leptin were within the normal range, thus ruling out insulin or leptin resistance. Consistently, instrumental investigations (X-ray and ultrasound analyses) documented no sign of glycogen accumulation in the internal organs. Consistently, the absence of significant changes in lipid storage was demonstrated by thin-layer chromatography (HPTLC) analysis in proband-derived fibroblast (Figure S1), allowing to confirm an apparently normal endocrine–metabolic profile in the affected individual. Of note, the Tubby protein has been involved in cochlear degeneration [20,21]. Based on this functional link, we evaluated the occurrence of hearing problems and cochlear degeneration, which were not observed.
+The homozygousTUBvariant was predicted to affect transcript processing, causing the skipping of exon 11 and intron retention, resulting in a frameshift with the premature termination of the TUB protein. mRNA analysis in proband-derived fibroblasts confirmed a disruptive impact of the splice site change documenting two aberrantly processed transcripts predicted to encode a 406-residue-long protein (p.Glu406Argfs*4) that probably is not able to proceed in protein synthesis, and a 481-residue-long protein (p.Pro463Hisfs*19) characterized by a divergent C-terminus characterized by accelerated degradation (Figure 3B). These findings confirm LoF as the pathomechanism underlying this disorder.
+Primary cilia are microtubule-based organelles that extend from the apical surface of the majority of mammalian cells. Cilia act as “cellular antennae”, receiving different inputs from the extracellular environment and transducing signals in response to stimuli [22]. A complex process required for proper cilia biogenesis function is the intraflagellar transport, which is required for assembling cilia and trafficking within primary cilia [23]. In this context, IFT-A has historically been believed to mediate retrograde intraflagellar transport inside the cilia and an IFT-A-binding domain at the TUB N-terminus has been demonstrated recently [24]. Moreover, co-localization between TUB and rootletin, the major structural component of the ciliary rootlet, has been observed in human retinal photoreceptors [10]. The use of a more informative in vitro model (e.g., induced pluripotent-stem-cell-derived retinal-pigment epithelium cells) and experimental strategies (e.g., siRNA-mediated TUB silencing) is required to appreciate more accurately the functional relevance of TUB in an appropriate cellular context.
+In summary, we confirm the link between TUB LoF and a new condition of human retinal ciliopathy and provide evidence of an altered cilium morphology/biogenesis in patient-derived fibroblasts. In fact, these cells displayed a reduced number of cilia when compared to the control cells, with a poorly defined and disorganized basal body structure, which are expected to prevent normal protein trafficking along the cilium. While these findings could explain the degeneration of photoreceptors characterizing this disorder, a relatively overall mild presentation has been associated with mutations in this gene. Multiple factors might contribute to this picture. First, the functional relevance of TUB in the context of ciliogenesis and cilium function might vary in different cell lineages. Second, functional compensation exerted by other related proteins might contribute to buffer the severity of the endophenotype. Third, specific cell lineages (e.g., rod and cone cells) might be particularly sensitive to TUB LoF. The collection of additional patients with biallelic variants in the gene will allow a more accurate characterization of the clinical spectrum associated with TUB LoF. Based on these considerations, TUB loss of function could be considered as responsible for a novel form of isolated retinal ciliopathy.</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>{
-"pmid": "36650547",
+"pmid": "9390831",
 "alias_symbol": "rd5",
 "primary_gene_symbol": "TUB",
 "name": "TUB bipartite transcription factor",
-"alias_symbol_represents_primary_gene": "YES",
 "alternate_abbreviation": "NO",
-"evidence": "TUB (MIM #601197), also known as rd5 or RDOB, maps to 11p15.4 and encodes the tubby-bipartite transcription regulator [10,11]."
+"evidence": ""
 }</t>
         </is>
       </c>

--- a/output/test_alt_abbrev_annotation_with_prompt_using_fulltext_and_abstract_df.xlsx
+++ b/output/test_alt_abbrev_annotation_with_prompt_using_fulltext_and_abstract_df.xlsx
@@ -456,57 +456,57 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>captured</t>
+          <t>captured_status</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>captured as:</t>
+          <t>captured_category_list</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>PMIDs from Pubtator3</t>
+          <t>pubtator3_pmid</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Does alias represent gene in this publication?</t>
+          <t>alias_represent_gene_status</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>As an Alternate Abbreviation?</t>
+          <t>alternate_abbreviation_status</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>How? I</t>
+          <t>simple_relationship_type</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>How? II</t>
+          <t>detailed_relationship_type</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>If not this gene, what is it?</t>
+          <t>alias_representation_details</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Text Location</t>
+          <t>relevant_text_section</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Relevant Text (surrounding)</t>
+          <t>relevant_text</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -575,15 +575,11 @@
       <c r="H2" t="n">
         <v>7479945</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -595,11 +591,7 @@
           <t>mouse phenotype biomarker</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -661,9 +653,9 @@
     Primary gene symbol: A1CF
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
-    "alternate_abbreviation": "NO"
+    "alternate_abbreviation": "FALSE"
     "evidence": ""
-    If the text does support that the alias is an alternate abbreviation, set "alternate_abbreviation": "YES"
+    If the text does support that the alias is an alternate abbreviation, set "alternate_abbreviation": "TRUE"
     Evidence must be one exact sentence copied verbatim from the text.
     Do not infer relationships or paraphrase evidence.
     Output (Strict):
@@ -673,7 +665,7 @@
     "alias_symbol": "",
     "primary_gene_symbol": "",
     "name": "",
-    "alternate_abbreviation": "YES or NO",
+    "alternate_abbreviation": "TRUE or FALSE",
     "evidence": ""
     }
 PMID: 7479945
@@ -687,7 +679,7 @@
 "alias_symbol": "rd5",
 "primary_gene_symbol": "TUB",
 "name": "TUB bipartite transcription factor",
-"alternate_abbreviation": "NO",
+"alternate_abbreviation": "FALSE",
 "evidence": ""
 }</t>
         </is>
@@ -728,15 +720,11 @@
       <c r="H3" t="n">
         <v>9390831</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -748,11 +736,7 @@
           <t>mouse phenotype biomarker</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>abstract</t>
@@ -854,9 +838,9 @@
     Primary gene symbol: A1CF
     Rules:
     If the text does not support that the alias is an alternate abbreviation, return:
-    "alternate_abbreviation": "NO"
+    "alternate_abbreviation": "FALSE"
     "evidence": ""
-    If the text does support that the alias is an alternate abbreviation, set "alternate_abbreviation": "YES"
+    If the text does support that the alias is an alternate abbreviation, set "alternate_abbreviation": "TRUE"
     Evidence must be one exact sentence copied verbatim from the text.
     Do not infer relationships or paraphrase evidence.
     Output (Strict):
@@ -866,7 +850,7 @@
     "alias_symbol": "",
     "primary_gene_symbol": "",
     "name": "",
-    "alternate_abbreviation": "YES or NO",
+    "alternate_abbreviation": "TRUE or FALSE",
     "evidence": ""
     }
 PMID: 9390831
@@ -898,7 +882,7 @@
 "alias_symbol": "rd5",
 "primary_gene_symbol": "TUB",
 "name": "TUB bipartite transcription factor",
-"alternate_abbreviation": "NO",
+"alternate_abbreviation": "FALSE",
 "evidence": ""
 }</t>
         </is>
